--- a/BANQUE_OFFICIELLE_NATURALISATION.xlsx
+++ b/BANQUE_OFFICIELLE_NATURALISATION.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timot\Documents\GitHub\Nova_Frate_PROTOTYPE_CHATMD_OPERATIONNEL\OUTILS_PYTHON\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\timot\Documents\GitHub\Chatbot_civique2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E10D177C-5110-4007-8A41-69A5C8C926A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2852E42D-24FF-4F10-AE79-F76507722C8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2861" uniqueCount="1343">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4577" uniqueCount="2081">
   <si>
     <t>ID</t>
   </si>
@@ -4068,6 +4068,2220 @@
   </si>
   <si>
     <t>📚 Thématique 3 – Justice 📖 Glossaire - Droits civiques - Éligibilité</t>
+  </si>
+  <si>
+    <t>NAT-T4-001</t>
+  </si>
+  <si>
+    <t>Histoire, géographie, patrimoine et culture</t>
+  </si>
+  <si>
+    <t>Histoire de France</t>
+  </si>
+  <si>
+    <t>Comment s'appelle le texte, promulgué en 1804 sous Napoléon Ier, qui rassemble les principales règles du droit civil français ?</t>
+  </si>
+  <si>
+    <t>La Constitution de 1958.</t>
+  </si>
+  <si>
+    <t>La Déclaration des droits de l'Homme.</t>
+  </si>
+  <si>
+    <t>Le Code civil, promulgué en 1804 sous Napoléon Ier, rassemble les principales règles du droit civil français (famille, propriété, contrats...). Il constitue l'un des fondements du droit français actuel.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Code civil = 1804, Napoléon Ier</t>
+  </si>
+  <si>
+    <t>Connaître les grandes étapes de l'histoire de France.</t>
+  </si>
+  <si>
+    <t>Napoléon; Code civil; 1804</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire de France 📖 Glossaire - Code civil</t>
+  </si>
+  <si>
+    <t>QUESTIONS_THEMATIQUE_4.md</t>
+  </si>
+  <si>
+    <t>NAT-T4-002</t>
+  </si>
+  <si>
+    <t>Lequel de ces noms est celui d'un Président de la Ve République ?</t>
+  </si>
+  <si>
+    <t>Napoléon Bonaparte.</t>
+  </si>
+  <si>
+    <t>Louis XIV.</t>
+  </si>
+  <si>
+    <t>Jules Ferry.</t>
+  </si>
+  <si>
+    <t>Georges Pompidou.</t>
+  </si>
+  <si>
+    <t>Depuis la création de la Ve République en 1958, plusieurs Présidents de la République se sont succédé, dont Charles de Gaulle, Georges Pompidou, Valéry Giscard d'Estaing, François Mitterrand, Jacques Chirac, Nicolas Sarkozy, François Hollande et Emmanuel Macron.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Présidents de la Ve République = de Gaulle à Macron</t>
+  </si>
+  <si>
+    <t>Connaître les principales figures politiques françaises.</t>
+  </si>
+  <si>
+    <t>Président; Ve République</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire politique 📖 Glossaire - Ve République</t>
+  </si>
+  <si>
+    <t>NAT-T4-003</t>
+  </si>
+  <si>
+    <t>Que célèbre la fête nationale française du 14 juillet ?</t>
+  </si>
+  <si>
+    <t>L'Armistice.</t>
+  </si>
+  <si>
+    <t>La Libération.</t>
+  </si>
+  <si>
+    <t>La Révolution de 1848.</t>
+  </si>
+  <si>
+    <t>La prise de la Bastille (1789).</t>
+  </si>
+  <si>
+    <t>Le 14 juillet est la fête nationale française. Elle commémore la prise de la Bastille (1789) et symbolise les valeurs de la République.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : 14 juillet = prise de la Bastille (1789)</t>
+  </si>
+  <si>
+    <t>Connaître les principales dates nationales.</t>
+  </si>
+  <si>
+    <t>14 juillet; Bastille; Fête nationale</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire 📖 Glossaire - Prise de la Bastille</t>
+  </si>
+  <si>
+    <t>NAT-T4-004</t>
+  </si>
+  <si>
+    <t>Quel était l'objectif principal des lois de Jules Ferry (1881-1882) ?</t>
+  </si>
+  <si>
+    <t>Supprimer l'école privée.</t>
+  </si>
+  <si>
+    <t>Créer les universités.</t>
+  </si>
+  <si>
+    <t>Rendre l'école payante.</t>
+  </si>
+  <si>
+    <t>Rendre l'école gratuite, laïque et obligatoire.</t>
+  </si>
+  <si>
+    <t>Les lois de Jules Ferry (1881-1882) rendent progressivement l'école primaire gratuite, laïque et obligatoire.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : lois Jules Ferry = gratuite, laïque, obligatoire</t>
+  </si>
+  <si>
+    <t>Connaître les grandes réformes de la République.</t>
+  </si>
+  <si>
+    <t>Jules Ferry; École; IIIe République</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire 📖 Glossaire - Lois Jules Ferry</t>
+  </si>
+  <si>
+    <t>NAT-T4-005</t>
+  </si>
+  <si>
+    <t>Pourquoi l'année 1958 est-elle importante dans l'histoire des institutions françaises ?</t>
+  </si>
+  <si>
+    <t>Début de la Première Guerre mondiale.</t>
+  </si>
+  <si>
+    <t>Création de l'Union européenne.</t>
+  </si>
+  <si>
+    <t>Révolution française.</t>
+  </si>
+  <si>
+    <t>Adoption de la Constitution qui fonde la Ve République.</t>
+  </si>
+  <si>
+    <t>La Constitution du 4 octobre 1958 fonde la Ve République. Elle organise les institutions françaises actuelles.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : 1958 = Constitution + Ve République</t>
+  </si>
+  <si>
+    <t>Connaître les grandes dates de l'histoire institutionnelle française.</t>
+  </si>
+  <si>
+    <t>1958; Ve République; Constitution</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire politique 📖 Glossaire - Constitution de 1958</t>
+  </si>
+  <si>
+    <t>NAT-T4-006</t>
+  </si>
+  <si>
+    <t>Quelle loi Simone Veil a-t-elle fait adopter en 1975 ?</t>
+  </si>
+  <si>
+    <t>La création de la Sécurité sociale.</t>
+  </si>
+  <si>
+    <t>L'abolition de la peine de mort.</t>
+  </si>
+  <si>
+    <t>La loi légalisant l'interruption volontaire de grossesse (IVG).</t>
+  </si>
+  <si>
+    <t>Survivante de la Shoah, Simone Veil est une grande figure de la République. Ministre de la Santé, elle a porté la loi de 1975 légalisant l'IVG. Elle a également été la première présidente du Parlement européen élue au suffrage universel.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Simone Veil = loi IVG (1975)</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures de l'histoire contemporaine.</t>
+  </si>
+  <si>
+    <t>Simone Veil; IVG; 1975; Parlement européen</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire contemporaine 📖 Glossaire - Simone Veil - IVG</t>
+  </si>
+  <si>
+    <t>NAT-T4-007</t>
+  </si>
+  <si>
+    <t>Union européenne et relations internationales</t>
+  </si>
+  <si>
+    <t>Lequel de ces pays est l'un des six pays fondateurs de la construction européenne ?</t>
+  </si>
+  <si>
+    <t>Espagne.</t>
+  </si>
+  <si>
+    <t>Croatie.</t>
+  </si>
+  <si>
+    <t>Pologne.</t>
+  </si>
+  <si>
+    <t>Italie.</t>
+  </si>
+  <si>
+    <t>Les six États fondateurs (France, Allemagne, Italie, Belgique, Pays-Bas, Luxembourg) sont à l'origine de la construction européenne avec la Communauté européenne du charbon et de l'acier (CECA) en 1951.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : 6 pays fondateurs = France, Allemagne, Italie, Belgique, Pays-Bas, Luxembourg</t>
+  </si>
+  <si>
+    <t>Connaître les origines de la construction européenne.</t>
+  </si>
+  <si>
+    <t>Union européenne; CECA; Pays fondateurs</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Construction européenne 📖 Glossaire - CECA</t>
+  </si>
+  <si>
+    <t>NAT-T4-008</t>
+  </si>
+  <si>
+    <t>Sur quelle région française a eu lieu le Débarquement allié du 6 juin 1944 ?</t>
+  </si>
+  <si>
+    <t>Bretagne.</t>
+  </si>
+  <si>
+    <t>Hauts-de-France.</t>
+  </si>
+  <si>
+    <t>Provence.</t>
+  </si>
+  <si>
+    <t>Normandie.</t>
+  </si>
+  <si>
+    <t>Le Débarquement du 6 juin 1944 a eu lieu sur plusieurs plages de Normandie. Il marque le début de la libération de la France occupée.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Débarquement (6 juin 1944) = Normandie</t>
+  </si>
+  <si>
+    <t>Connaître les grands événements de la Seconde Guerre mondiale.</t>
+  </si>
+  <si>
+    <t>Normandie; Débarquement; 1944</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Seconde Guerre mondiale 📖 Glossaire - Débarquement de Normandie</t>
+  </si>
+  <si>
+    <t>NAT-T4-009</t>
+  </si>
+  <si>
+    <t>Dans quelle ville les rois de France étaient-ils traditionnellement sacrés ?</t>
+  </si>
+  <si>
+    <t>Paris.</t>
+  </si>
+  <si>
+    <t>Versailles.</t>
+  </si>
+  <si>
+    <t>Orléans.</t>
+  </si>
+  <si>
+    <t>Reims.</t>
+  </si>
+  <si>
+    <t>La cathédrale de Reims a accueilli le sacre de la grande majorité des rois de France, faisant de cette ville un lieu symbolique de la monarchie française.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : sacre des rois = Reims</t>
+  </si>
+  <si>
+    <t>Connaître les grands lieux historiques de la monarchie française.</t>
+  </si>
+  <si>
+    <t>Reims; Cathédrale; Monarchie; Sacre</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire de France 📖 Glossaire - Sacre des rois</t>
+  </si>
+  <si>
+    <t>NAT-T4-010</t>
+  </si>
+  <si>
+    <t>Qui est l'auteur des grandes lois scolaires de la IIIᵉ République rendant l'école gratuite, laïque et obligatoire ?</t>
+  </si>
+  <si>
+    <t>Napoléon.</t>
+  </si>
+  <si>
+    <t>Charles de Gaulle.</t>
+  </si>
+  <si>
+    <t>Jules Ferry est l'auteur des grandes lois scolaires de la IIIᵉ République. Elles garantissent l'accès de tous les enfants à une école publique gratuite, laïque et obligatoire.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : lois scolaires (1881-1882) = Jules Ferry</t>
+  </si>
+  <si>
+    <t>Jules Ferry; École; 1881; 1882; IIIe République</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire de France 📖 Glossaire - Jules Ferry - Lois scolaires</t>
+  </si>
+  <si>
+    <t>NAT-T4-011</t>
+  </si>
+  <si>
+    <t>Quel roi de France a été guillotiné le 21 janvier 1793 pendant la Révolution ?</t>
+  </si>
+  <si>
+    <t>Louis XV.</t>
+  </si>
+  <si>
+    <t>Napoléon Ier.</t>
+  </si>
+  <si>
+    <t>Louis XVI.</t>
+  </si>
+  <si>
+    <t>Louis XVI est le dernier roi de l'Ancien Régime. Il est guillotiné le 21 janvier 1793 pendant la Révolution française.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : roi guillotiné en 1793 = Louis XVI</t>
+  </si>
+  <si>
+    <t>Connaître les grands événements de la Révolution française.</t>
+  </si>
+  <si>
+    <t>Louis XVI; Révolution française; 1793; Guillotine</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Révolution française 📖 Glossaire - Louis XVI</t>
+  </si>
+  <si>
+    <t>NAT-T4-012</t>
+  </si>
+  <si>
+    <t>En quelle année a débuté la Révolution française ?</t>
+  </si>
+  <si>
+    <t>1792.</t>
+  </si>
+  <si>
+    <t>1804.</t>
+  </si>
+  <si>
+    <t>1815.</t>
+  </si>
+  <si>
+    <t>La Révolution française débute en 1789. Cette année marque notamment la prise de la Bastille le 14 juillet et l'adoption de la Déclaration des droits de l'Homme et du Citoyen.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Révolution française = 1789</t>
+  </si>
+  <si>
+    <t>Connaître les grandes dates de l'histoire de France.</t>
+  </si>
+  <si>
+    <t>1789; Révolution française; Bastille</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Révolution française 📖 Glossaire - Révolution française</t>
+  </si>
+  <si>
+    <t>NAT-T4-013</t>
+  </si>
+  <si>
+    <t>En quelle année Napoléon Bonaparte est-il devenu empereur des Français ?</t>
+  </si>
+  <si>
+    <t>1799.</t>
+  </si>
+  <si>
+    <t>Napoléon Bonaparte devient empereur des Français en 1804. Son sacre a lieu le 2 décembre 1804 à Notre-Dame de Paris.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Napoléon empereur = 1804</t>
+  </si>
+  <si>
+    <t>Napoléon; 1804; Empire</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Premier Empire 📖 Glossaire - Napoléon Ier</t>
+  </si>
+  <si>
+    <t>NAT-T4-014</t>
+  </si>
+  <si>
+    <t>Quel homme d'État a fait adopter des lois rendant l'école laïque, gratuite et obligatoire pour les enfants de 6 à 13 ans ?</t>
+  </si>
+  <si>
+    <t>Jules Ferry est un homme d'État français. Il a fait adopter des lois qui rendent l'école laïque, gratuite et obligatoire pour tous les enfants âgés de 6 à 13 ans.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : école laïque, gratuite, obligatoire (6-13 ans) = Jules Ferry</t>
+  </si>
+  <si>
+    <t>Connaître les grandes réformes scolaires de la République.</t>
+  </si>
+  <si>
+    <t>Jules Ferry; École; Instruction obligatoire</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire de France 📖 Glossaire - Jules Ferry</t>
+  </si>
+  <si>
+    <t>NAT-T4-015</t>
+  </si>
+  <si>
+    <t>À quelle date le général de Gaulle a-t-il lancé son appel à la Résistance depuis Londres ?</t>
+  </si>
+  <si>
+    <t>8 mai 1945.</t>
+  </si>
+  <si>
+    <t>6 juin 1944.</t>
+  </si>
+  <si>
+    <t>11 novembre 1918.</t>
+  </si>
+  <si>
+    <t>Le 18 juin 1940.</t>
+  </si>
+  <si>
+    <t>Le 18 juin 1940, depuis Londres, le général de Gaulle lance un appel à poursuivre le combat contre l'Allemagne nazie. Cet appel est devenu le symbole de la Résistance française.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : appel à la Résistance = 18 juin 1940</t>
+  </si>
+  <si>
+    <t>Connaître les grandes dates de la Seconde Guerre mondiale.</t>
+  </si>
+  <si>
+    <t>18 juin 1940; Charles de Gaulle; Résistance</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Seconde Guerre mondiale 📖 Glossaire - Appel du 18 juin</t>
+  </si>
+  <si>
+    <t>NAT-T4-016</t>
+  </si>
+  <si>
+    <t>Qu'est-ce que la Shoah ?</t>
+  </si>
+  <si>
+    <t>Une bataille.</t>
+  </si>
+  <si>
+    <t>La Première Guerre mondiale.</t>
+  </si>
+  <si>
+    <t>L'extermination des Juifs d'Europe par le régime nazi.</t>
+  </si>
+  <si>
+    <t>La Shoah désigne l'extermination systématique d'environ six millions de Juifs par le régime nazi entre 1941 et 1945. Son étude participe au devoir de mémoire et à la lutte contre l'antisémitisme et le racisme.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Shoah = extermination des Juifs par le régime nazi</t>
+  </si>
+  <si>
+    <t>Connaître les grands événements de l'histoire contemporaine.</t>
+  </si>
+  <si>
+    <t>Shoah; Génocide; Nazisme; Seconde Guerre mondiale</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Seconde Guerre mondiale 📖 Glossaire - Shoah - Génocide</t>
+  </si>
+  <si>
+    <t>NAT-T4-017</t>
+  </si>
+  <si>
+    <t>Culture et patrimoine</t>
+  </si>
+  <si>
+    <t>Laquelle de ces œuvres a été écrite par Victor Hugo ?</t>
+  </si>
+  <si>
+    <t>Le Petit Prince.</t>
+  </si>
+  <si>
+    <t>Madame Bovary.</t>
+  </si>
+  <si>
+    <t>Germinal.</t>
+  </si>
+  <si>
+    <t>Les Misérables.</t>
+  </si>
+  <si>
+    <t>Victor Hugo est l'un des plus grands écrivains français. Parmi ses œuvres les plus célèbres figurent Les Misérables et Notre-Dame de Paris.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Victor Hugo = Les Misérables, Notre-Dame de Paris</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures de la littérature française.</t>
+  </si>
+  <si>
+    <t>Victor Hugo; Les Misérables; Notre-Dame de Paris</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Culture 📖 Glossaire - Victor Hugo</t>
+  </si>
+  <si>
+    <t>NAT-T4-018</t>
+  </si>
+  <si>
+    <t>Citez un pays ayant été colonisé par la France.</t>
+  </si>
+  <si>
+    <t>Allemagne.</t>
+  </si>
+  <si>
+    <t>Japon.</t>
+  </si>
+  <si>
+    <t>Algérie.</t>
+  </si>
+  <si>
+    <t>La France a constitué un vaste empire colonial, notamment en Afrique, en Asie et dans les Caraïbes. Plusieurs pays actuels (Algérie, Maroc, Tunisie, Sénégal, Vietnam, Côte d'Ivoire, Madagascar...) ont été des colonies ou des protectorats français.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : empire colonial français = Algérie, Sénégal, Madagascar, Indochine...</t>
+  </si>
+  <si>
+    <t>Connaître l'histoire de la France.</t>
+  </si>
+  <si>
+    <t>Colonisation; Empire colonial; Algérie; Afrique</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire de France 📖 Glossaire - Colonisation</t>
+  </si>
+  <si>
+    <t>NAT-T4-019</t>
+  </si>
+  <si>
+    <t>Depuis quelle année les Français élisent-ils le Président de la République au suffrage universel direct ?</t>
+  </si>
+  <si>
+    <t>1962.</t>
+  </si>
+  <si>
+    <t>Le référendum de 1962, voulu par le général de Gaulle, instaure l'élection du Président de la République au suffrage universel direct.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Président élu au suffrage universel direct = depuis 1962</t>
+  </si>
+  <si>
+    <t>Connaître les grandes étapes de la Ve République.</t>
+  </si>
+  <si>
+    <t>1962; Suffrage universel; Président; Charles de Gaulle</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Institutions 📖 Glossaire - Suffrage universel direct</t>
+  </si>
+  <si>
+    <t>NAT-T4-020</t>
+  </si>
+  <si>
+    <t>En quelle année l'Union européenne a-t-elle été officiellement créée par le traité de Maastricht ?</t>
+  </si>
+  <si>
+    <t>L'Union européenne est officiellement créée par le traité de Maastricht, signé en 1992. Ce traité instaure également la citoyenneté européenne.</t>
+  </si>
+  <si>
+    <t>1992; Union européenne; Maastricht</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Construction européenne 📖 Glossaire - Traité de Maastricht</t>
+  </si>
+  <si>
+    <t>NAT-T4-021</t>
+  </si>
+  <si>
+    <t>De quand à quand s'est déroulée la Seconde Guerre mondiale ?</t>
+  </si>
+  <si>
+    <t>1914-1918.</t>
+  </si>
+  <si>
+    <t>1940-1944.</t>
+  </si>
+  <si>
+    <t>1938-1946.</t>
+  </si>
+  <si>
+    <t>De 1939 à 1945.</t>
+  </si>
+  <si>
+    <t>La Seconde Guerre mondiale s'est déroulée de 1939 à 1945. Elle a profondément marqué la France, l'Europe et le monde.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Seconde Guerre mondiale = 1939-1945</t>
+  </si>
+  <si>
+    <t>Connaître les grandes périodes de l'histoire.</t>
+  </si>
+  <si>
+    <t>1939; 1945; Seconde Guerre mondiale</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire contemporaine 📖 Glossaire - Seconde Guerre mondiale</t>
+  </si>
+  <si>
+    <t>NAT-T4-022</t>
+  </si>
+  <si>
+    <t>De quand à quand s'est déroulée la Première Guerre mondiale ?</t>
+  </si>
+  <si>
+    <t>1939-1945.</t>
+  </si>
+  <si>
+    <t>1789-1799.</t>
+  </si>
+  <si>
+    <t>1918-1945.</t>
+  </si>
+  <si>
+    <t>De 1914 à 1918.</t>
+  </si>
+  <si>
+    <t>La Première Guerre mondiale oppose principalement les puissances alliées aux Empires centraux entre 1914 et 1918.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Première Guerre mondiale = 1914-1918</t>
+  </si>
+  <si>
+    <t>1914; 1918; Première Guerre mondiale</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire contemporaine 📖 Glossaire - Première Guerre mondiale</t>
+  </si>
+  <si>
+    <t>NAT-T4-023</t>
+  </si>
+  <si>
+    <t>Sous la présidence de qui la peine de mort a-t-elle été abolie en France, en 1981 ?</t>
+  </si>
+  <si>
+    <t>Jacques Chirac.</t>
+  </si>
+  <si>
+    <t>Valéry Giscard d'Estaing.</t>
+  </si>
+  <si>
+    <t>François Mitterrand.</t>
+  </si>
+  <si>
+    <t>La peine de mort est abolie en 1981, sous la présidence de François Mitterrand, grâce au projet défendu par le garde des Sceaux Robert Badinter.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : abolition peine de mort (1981) = François Mitterrand + Robert Badinter</t>
+  </si>
+  <si>
+    <t>Connaître les grandes réformes de la Ve République.</t>
+  </si>
+  <si>
+    <t>François Mitterrand; Robert Badinter; 1981; Peine de mort</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire contemporaine 📖 Glossaire - Abolition de la peine de mort</t>
+  </si>
+  <si>
+    <t>NAT-T4-024</t>
+  </si>
+  <si>
+    <t>Que commémore le 8 mai, jour férié en France ?</t>
+  </si>
+  <si>
+    <t>L'Armistice de 1918.</t>
+  </si>
+  <si>
+    <t>Le Débarquement.</t>
+  </si>
+  <si>
+    <t>La Révolution française.</t>
+  </si>
+  <si>
+    <t>La victoire des Alliés sur l'Allemagne nazie en 1945.</t>
+  </si>
+  <si>
+    <t>Le 8 mai est un jour férié en France. Il commémore la victoire des Alliés en 1945 et rend hommage aux combattants de la Seconde Guerre mondiale.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : 8 mai = victoire des Alliés (1945)</t>
+  </si>
+  <si>
+    <t>8 mai; 1945; Victoire; Commémoration</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Commémorations nationales 📖 Glossaire - Victoire du 8 mai 1945</t>
+  </si>
+  <si>
+    <t>NAT-T4-025</t>
+  </si>
+  <si>
+    <t>Quelle est la première étape de la construction européenne, créée en 1951 ?</t>
+  </si>
+  <si>
+    <t>L'Union européenne.</t>
+  </si>
+  <si>
+    <t>L'euro.</t>
+  </si>
+  <si>
+    <t>La Communauté européenne du charbon et de l'acier (CECA).</t>
+  </si>
+  <si>
+    <t>Créée en 1951, la CECA constitue la première étape de la construction européenne. Elle réunit six États fondateurs afin de favoriser la paix et la coopération économique.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : première étape de la construction européenne = CECA (1951)</t>
+  </si>
+  <si>
+    <t>CECA; 1951; Union européenne; Construction européenne</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Construction européenne 📖 Glossaire - CECA - États fondateurs</t>
+  </si>
+  <si>
+    <t>NAT-T4-026</t>
+  </si>
+  <si>
+    <t>Qui a été chargé par le général de Gaulle d'unifier les mouvements de Résistance ?</t>
+  </si>
+  <si>
+    <t>Jean Moulin.</t>
+  </si>
+  <si>
+    <t>Jean Moulin est chargé par le général de Gaulle d'unifier les mouvements de Résistance. Arrêté en 1943, il meurt sous la torture sans avoir livré d'informations.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : unification de la Résistance = Jean Moulin</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures de la Seconde Guerre mondiale.</t>
+  </si>
+  <si>
+    <t>Jean Moulin; Résistance; Seconde Guerre mondiale; Charles de Gaulle</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Seconde Guerre mondiale 📖 Glossaire - Jean Moulin</t>
+  </si>
+  <si>
+    <t>NAT-T4-027</t>
+  </si>
+  <si>
+    <t>Géographie</t>
+  </si>
+  <si>
+    <t>Quelle mer sépare la France de l'Angleterre ?</t>
+  </si>
+  <si>
+    <t>La mer du Nord.</t>
+  </si>
+  <si>
+    <t>La Méditerranée.</t>
+  </si>
+  <si>
+    <t>L'océan Atlantique.</t>
+  </si>
+  <si>
+    <t>La Manche.</t>
+  </si>
+  <si>
+    <t>La Manche sépare la France et l'Angleterre. C'est également sous cette mer que passe le tunnel sous la Manche.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : France-Angleterre = la Manche</t>
+  </si>
+  <si>
+    <t>Connaître la géographie de la France.</t>
+  </si>
+  <si>
+    <t>La Manche; Angleterre; France</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - La Manche</t>
+  </si>
+  <si>
+    <t>NAT-T4-028</t>
+  </si>
+  <si>
+    <t>Que commémore le 11 novembre, jour férié en France ?</t>
+  </si>
+  <si>
+    <t>La Libération de Paris.</t>
+  </si>
+  <si>
+    <t>Le 8 mai 1945.</t>
+  </si>
+  <si>
+    <t>L'Armistice de la Première Guerre mondiale (1918).</t>
+  </si>
+  <si>
+    <t>Le 11 novembre commémore l'Armistice signé en 1918, qui met fin aux combats de la Première Guerre mondiale.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : 11 novembre = Armistice de 1918</t>
+  </si>
+  <si>
+    <t>Connaître les commémorations nationales.</t>
+  </si>
+  <si>
+    <t>11 novembre; Armistice; 1918; Première Guerre mondiale</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Commémorations nationales 📖 Glossaire - Armistice</t>
+  </si>
+  <si>
+    <t>NAT-T4-029</t>
+  </si>
+  <si>
+    <t>Depuis quelle année l'esclavage est-il définitivement aboli en France ?</t>
+  </si>
+  <si>
+    <t>Depuis 1848.</t>
+  </si>
+  <si>
+    <t>L'esclavage est définitivement aboli en France par le décret du 27 avril 1848.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : abolition de l'esclavage = 1848</t>
+  </si>
+  <si>
+    <t>1848; Esclavage; Abolition</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire de France 📖 Glossaire - Abolition de l'esclavage</t>
+  </si>
+  <si>
+    <t>NAT-T4-030</t>
+  </si>
+  <si>
+    <t>Qui est le principal artisan du décret de 1848 abolissant l'esclavage dans les colonies françaises ?</t>
+  </si>
+  <si>
+    <t>Victor Schœlcher.</t>
+  </si>
+  <si>
+    <t>Victor Schœlcher est le principal artisan du décret de 1848 abolissant définitivement l'esclavage dans les colonies françaises.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : abolition de l'esclavage (1848) = Victor Schœlcher</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures de l'histoire de France.</t>
+  </si>
+  <si>
+    <t>Victor Schœlcher; 1848; Esclavage; Abolition</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire de France 📖 Glossaire - Victor Schœlcher</t>
+  </si>
+  <si>
+    <t>NAT-T4-031</t>
+  </si>
+  <si>
+    <t>Depuis quelle année l'école primaire publique est-elle gratuite en France ?</t>
+  </si>
+  <si>
+    <t>1882.</t>
+  </si>
+  <si>
+    <t>Depuis 1881.</t>
+  </si>
+  <si>
+    <t>La loi du 16 juin 1881 rend l'école primaire publique gratuite. En 1882, Jules Ferry rend l'instruction obligatoire et l'enseignement public laïque.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : école gratuite = 1881 (obligatoire en 1882)</t>
+  </si>
+  <si>
+    <t>Connaître les grandes réformes de la IIIᵉ République.</t>
+  </si>
+  <si>
+    <t>1881; Jules Ferry; École gratuite</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire de France 📖 Glossaire - Lois Jules Ferry</t>
+  </si>
+  <si>
+    <t>NAT-T4-032</t>
+  </si>
+  <si>
+    <t>Quelle chaîne de montagnes forme la frontière naturelle entre la France et l'Espagne ?</t>
+  </si>
+  <si>
+    <t>Les Alpes.</t>
+  </si>
+  <si>
+    <t>Le Massif central.</t>
+  </si>
+  <si>
+    <t>Les Vosges.</t>
+  </si>
+  <si>
+    <t>Les Pyrénées.</t>
+  </si>
+  <si>
+    <t>Les Pyrénées forment la frontière naturelle entre la France et l'Espagne sur près de 430 kilomètres.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : frontière France-Espagne = les Pyrénées</t>
+  </si>
+  <si>
+    <t>Pyrénées; Espagne; Montagnes</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Pyrénées</t>
+  </si>
+  <si>
+    <t>NAT-T4-033</t>
+  </si>
+  <si>
+    <t>Qu'ont obtenu les femmes françaises grâce à l'ordonnance du 21 avril 1944 ?</t>
+  </si>
+  <si>
+    <t>Elles deviennent députées automatiquement.</t>
+  </si>
+  <si>
+    <t>Elles obtiennent le droit au divorce.</t>
+  </si>
+  <si>
+    <t>Elles deviennent majeures à 18 ans.</t>
+  </si>
+  <si>
+    <t>Elles ont obtenu le droit de vote.</t>
+  </si>
+  <si>
+    <t>Le 21 avril 1944, les femmes obtiennent le droit de vote et d'éligibilité. Elles votent pour la première fois lors des élections municipales de 1945.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : 21 avril 1944 = droit de vote des femmes</t>
+  </si>
+  <si>
+    <t>Connaître les grandes avancées des droits civiques.</t>
+  </si>
+  <si>
+    <t>1944; Femmes; Droit de vote; Éligibilité</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire contemporaine 📖 Glossaire - Suffrage féminin</t>
+  </si>
+  <si>
+    <t>NAT-T4-034</t>
+  </si>
+  <si>
+    <t>Quelle organisation internationale a été créée en 1945 pour maintenir la paix dans le monde ?</t>
+  </si>
+  <si>
+    <t>L'OTAN.</t>
+  </si>
+  <si>
+    <t>La CECA.</t>
+  </si>
+  <si>
+    <t>L'Organisation des Nations unies (ONU).</t>
+  </si>
+  <si>
+    <t>L'Organisation des Nations unies (ONU) est créée en 1945 afin de maintenir la paix et favoriser la coopération internationale après la Seconde Guerre mondiale.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : ONU = 1945</t>
+  </si>
+  <si>
+    <t>Connaître les principales organisations internationales.</t>
+  </si>
+  <si>
+    <t>ONU; 1945; Nations unies</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Relations internationales 📖 Glossaire - ONU</t>
+  </si>
+  <si>
+    <t>NAT-T4-035</t>
+  </si>
+  <si>
+    <t>En quelle année les pièces et billets en euros sont-ils entrés en circulation en France ?</t>
+  </si>
+  <si>
+    <t>1999.</t>
+  </si>
+  <si>
+    <t>2000.</t>
+  </si>
+  <si>
+    <t>L'euro est introduit sous forme scripturale en 1999, mais les pièces et billets entrent en circulation le 1er janvier 2002, remplaçant le franc.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : pièces/billets en euros = 2002</t>
+  </si>
+  <si>
+    <t>Euro; 2002; Monnaie; France</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Construction européenne 📖 Glossaire - Euro</t>
+  </si>
+  <si>
+    <t>NAT-T4-036</t>
+  </si>
+  <si>
+    <t>À quelle date Paris a-t-elle été libérée en 1944 ?</t>
+  </si>
+  <si>
+    <t>Le 6 juin.</t>
+  </si>
+  <si>
+    <t>Le 25 août.</t>
+  </si>
+  <si>
+    <t>Le 25 août 1944, Paris est libérée par les Forces françaises de l'intérieur et la 2ᵉ Division blindée du général Leclerc. Cet événement marque une étape majeure de la Libération de la France.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Libération de Paris = 25 août 1944</t>
+  </si>
+  <si>
+    <t>Paris; 25 août 1944; Libération; Leclerc</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Seconde Guerre mondiale 📖 Glossaire - Libération de Paris</t>
+  </si>
+  <si>
+    <t>NAT-T4-037</t>
+  </si>
+  <si>
+    <t>Quel port français était, au XVIIIᵉ siècle, le principal port impliqué dans la traite négrière ?</t>
+  </si>
+  <si>
+    <t>Marseille.</t>
+  </si>
+  <si>
+    <t>Bordeaux.</t>
+  </si>
+  <si>
+    <t>Le Havre.</t>
+  </si>
+  <si>
+    <t>Nantes.</t>
+  </si>
+  <si>
+    <t>Au XVIIIᵉ siècle, Nantes est le principal port français impliqué dans la traite négrière. Cette histoire est aujourd'hui reconnue et fait l'objet d'un important travail de mémoire.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : principal port de la traite négrière = Nantes</t>
+  </si>
+  <si>
+    <t>Connaître les grandes pages de l'histoire de France.</t>
+  </si>
+  <si>
+    <t>Nantes; Traite négrière; Esclavage</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Histoire de France 📖 Glossaire - Traite négrière</t>
+  </si>
+  <si>
+    <t>NAT-T4-038</t>
+  </si>
+  <si>
+    <t>Quel philosophe des Lumières est identifié, dans cette question, comme ayant critiqué l'esclavage et défendu la liberté et la tolérance ?</t>
+  </si>
+  <si>
+    <t>Rousseau.</t>
+  </si>
+  <si>
+    <t>Montesquieu.</t>
+  </si>
+  <si>
+    <t>Diderot.</t>
+  </si>
+  <si>
+    <t>Voltaire.</t>
+  </si>
+  <si>
+    <t>Voltaire est l'une des grandes figures du siècle des Lumières. Il critique l'esclavage et défend les idées de liberté, de tolérance et de justice. Plusieurs philosophes des Lumières ont critiqué l'esclavage, mais la réponse officiellement attendue pour cet examen est Voltaire.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : critique de l'esclavage (Lumières) = Voltaire</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures intellectuelles françaises.</t>
+  </si>
+  <si>
+    <t>Voltaire; Lumières; Esclavage</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Culture et Histoire 📖 Glossaire - Siècle des Lumières</t>
+  </si>
+  <si>
+    <t>NAT-T4-039</t>
+  </si>
+  <si>
+    <t>Lequel de ces peintres est français ?</t>
+  </si>
+  <si>
+    <t>Pablo Picasso.</t>
+  </si>
+  <si>
+    <t>Léonard de Vinci.</t>
+  </si>
+  <si>
+    <t>Vincent Van Gogh.</t>
+  </si>
+  <si>
+    <t>Claude Monet.</t>
+  </si>
+  <si>
+    <t>La France compte de nombreux peintres mondialement connus, notamment les impressionnistes comme Claude Monet, Auguste Renoir ou Edgar Degas.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : peintres français = Monet, Renoir, Degas, Cézanne...</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures artistiques françaises.</t>
+  </si>
+  <si>
+    <t>Peinture; Monet; Renoir; Cézanne</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Arts 📖 Glossaire - Impressionnisme</t>
+  </si>
+  <si>
+    <t>NAT-T4-040</t>
+  </si>
+  <si>
+    <t>Laquelle de ces spécialités est un plat traditionnel français ?</t>
+  </si>
+  <si>
+    <t>Pizza.</t>
+  </si>
+  <si>
+    <t>Sushi.</t>
+  </si>
+  <si>
+    <t>Paella.</t>
+  </si>
+  <si>
+    <t>Le cassoulet.</t>
+  </si>
+  <si>
+    <t>La gastronomie est un élément important du patrimoine français. Elle est reconnue par l'UNESCO à travers le repas gastronomique des Français, inscrit au patrimoine culturel immatériel de l'humanité.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : gastronomie française = repas gastronomique inscrit à l'UNESCO</t>
+  </si>
+  <si>
+    <t>Connaître les éléments majeurs de la culture française.</t>
+  </si>
+  <si>
+    <t>Cuisine; Gastronomie; Patrimoine; France</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Culture 📖 Glossaire - Gastronomie française</t>
+  </si>
+  <si>
+    <t>NAT-T4-041</t>
+  </si>
+  <si>
+    <t>Qui était Marie Curie ?</t>
+  </si>
+  <si>
+    <t>Une écrivaine.</t>
+  </si>
+  <si>
+    <t>Une reine de France.</t>
+  </si>
+  <si>
+    <t>Une peintre.</t>
+  </si>
+  <si>
+    <t>Une scientifique franco-polonaise, double prix Nobel.</t>
+  </si>
+  <si>
+    <t>Marie Curie est l'une des plus grandes scientifiques de l'histoire. Elle est la première femme à recevoir un prix Nobel et la seule personne à avoir obtenu deux prix Nobel dans deux disciplines scientifiques différentes (physique et chimie).</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Marie Curie = scientifique franco-polonaise, deux prix Nobel</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures scientifiques.</t>
+  </si>
+  <si>
+    <t>Marie Curie; Prix Nobel; Radioactivité; Science</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Culture scientifique 📖 Glossaire - Marie Curie</t>
+  </si>
+  <si>
+    <t>NAT-T4-042</t>
+  </si>
+  <si>
+    <t>Qui a peint « La Liberté guidant le peuple » en 1830 ?</t>
+  </si>
+  <si>
+    <t>Auguste Renoir.</t>
+  </si>
+  <si>
+    <t>Paul Cézanne.</t>
+  </si>
+  <si>
+    <t>Eugène Delacroix.</t>
+  </si>
+  <si>
+    <t>« La Liberté guidant le peuple », peinte par Eugène Delacroix en 1830, est devenue un symbole de la République et de la liberté.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : « La Liberté guidant le peuple » = Eugène Delacroix</t>
+  </si>
+  <si>
+    <t>Connaître les grandes œuvres de la peinture française.</t>
+  </si>
+  <si>
+    <t>Delacroix; Liberté guidant le peuple; Peinture</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Arts 📖 Glossaire - Eugène Delacroix</t>
+  </si>
+  <si>
+    <t>NAT-T4-043</t>
+  </si>
+  <si>
+    <t>Où est exposée la Joconde de Léonard de Vinci ?</t>
+  </si>
+  <si>
+    <t>Le musée d'Orsay.</t>
+  </si>
+  <si>
+    <t>Le Centre Pompidou.</t>
+  </si>
+  <si>
+    <t>Le château de Versailles.</t>
+  </si>
+  <si>
+    <t>Le musée du Louvre.</t>
+  </si>
+  <si>
+    <t>La Joconde, peinte par Léonard de Vinci, est exposée au musée du Louvre, le plus grand musée de France et l'un des plus célèbres au monde.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Joconde = musée du Louvre</t>
+  </si>
+  <si>
+    <t>Connaître les principaux musées français.</t>
+  </si>
+  <si>
+    <t>Louvre; Joconde; Paris</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Patrimoine 📖 Glossaire - Musée du Louvre</t>
+  </si>
+  <si>
+    <t>NAT-T4-044</t>
+  </si>
+  <si>
+    <t>Quel monument est la résidence royale développée par Louis XIV, le Roi-Soleil ?</t>
+  </si>
+  <si>
+    <t>Fontainebleau.</t>
+  </si>
+  <si>
+    <t>Chambord.</t>
+  </si>
+  <si>
+    <t>Le Louvre.</t>
+  </si>
+  <si>
+    <t>Le château de Versailles est la résidence royale développée par Louis XIV, le Roi-Soleil. Il est aujourd'hui l'un des monuments les plus visités de France.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : résidence de Louis XIV = château de Versailles</t>
+  </si>
+  <si>
+    <t>Connaître les principaux monuments historiques français.</t>
+  </si>
+  <si>
+    <t>Versailles; Louis XIV; Roi-Soleil</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Patrimoine 📖 Glossaire - Château de Versailles</t>
+  </si>
+  <si>
+    <t>NAT-T4-045</t>
+  </si>
+  <si>
+    <t>Où se trouvent les célèbres peintures rupestres préhistoriques vieilles d'environ 17 000 ans ?</t>
+  </si>
+  <si>
+    <t>Au Louvre.</t>
+  </si>
+  <si>
+    <t>À Versailles.</t>
+  </si>
+  <si>
+    <t>Au Mont-Saint-Michel.</t>
+  </si>
+  <si>
+    <t>Dans la grotte de Lascaux.</t>
+  </si>
+  <si>
+    <t>La grotte de Lascaux, en Dordogne, est célèbre pour ses peintures rupestres datant d'environ 17 000 ans. Elle constitue l'un des plus grands témoignages de l'art préhistorique.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : peintures rupestres préhistoriques = grotte de Lascaux</t>
+  </si>
+  <si>
+    <t>Connaître le patrimoine historique français.</t>
+  </si>
+  <si>
+    <t>Lascaux; Préhistoire; Patrimoine</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Patrimoine 📖 Glossaire - Grotte de Lascaux</t>
+  </si>
+  <si>
+    <t>NAT-T4-046</t>
+  </si>
+  <si>
+    <t>Qui a peint la célèbre série des Nymphéas ?</t>
+  </si>
+  <si>
+    <t>Renoir.</t>
+  </si>
+  <si>
+    <t>Cézanne.</t>
+  </si>
+  <si>
+    <t>Delacroix.</t>
+  </si>
+  <si>
+    <t>Les Nymphéas sont une série de tableaux réalisés par Claude Monet, l'un des principaux représentants de l'impressionnisme. Une grande partie est exposée au musée de l'Orangerie à Paris.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Nymphéas = Claude Monet</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures de la peinture française.</t>
+  </si>
+  <si>
+    <t>Claude Monet; Nymphéas; Impressionnisme</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Arts 📖 Glossaire - Claude Monet</t>
+  </si>
+  <si>
+    <t>NAT-T4-047</t>
+  </si>
+  <si>
+    <t>Quel événement permet chaque année de visiter gratuitement de nombreux monuments habituellement payants ?</t>
+  </si>
+  <si>
+    <t>La Nuit des musées.</t>
+  </si>
+  <si>
+    <t>Les vacances scolaires.</t>
+  </si>
+  <si>
+    <t>Les Journées européennes du patrimoine.</t>
+  </si>
+  <si>
+    <t>Chaque année, les Journées européennes du patrimoine ouvrent gratuitement au public des milliers de monuments, musées et bâtiments habituellement fermés ou payants.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : visites gratuites de monuments = Journées européennes du patrimoine (septembre)</t>
+  </si>
+  <si>
+    <t>Connaître les événements culturels nationaux.</t>
+  </si>
+  <si>
+    <t>Patrimoine; Culture; Monuments; Septembre</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Culture 📖 Glossaire - Journées européennes du patrimoine</t>
+  </si>
+  <si>
+    <t>NAT-T4-048</t>
+  </si>
+  <si>
+    <t>Que célèbre-t-on le 1er mai en France ?</t>
+  </si>
+  <si>
+    <t>La fête nationale.</t>
+  </si>
+  <si>
+    <t>La fête du Travail.</t>
+  </si>
+  <si>
+    <t>Le 1er mai est la fête du Travail. C'est un jour férié en France, associé aux droits des travailleurs. Il est également traditionnel d'offrir du muguet ce jour-là.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : 1er mai = fête du Travail (muguet)</t>
+  </si>
+  <si>
+    <t>Connaître les principales fêtes civiles françaises.</t>
+  </si>
+  <si>
+    <t>1er mai; Travail; Muguet; Jour férié</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Commémorations 📖 Glossaire - Fête du Travail</t>
+  </si>
+  <si>
+    <t>NAT-T4-049</t>
+  </si>
+  <si>
+    <t>Qui est l'auteur de la Marseillaise ?</t>
+  </si>
+  <si>
+    <t>Beethoven.</t>
+  </si>
+  <si>
+    <t>Claude Joseph Rouget de Lisle.</t>
+  </si>
+  <si>
+    <t>Claude Joseph Rouget de Lisle compose La Marseillaise en 1792. Ce chant révolutionnaire devient ensuite l'hymne national de la République française.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : auteur de la Marseillaise = Rouget de Lisle (1792)</t>
+  </si>
+  <si>
+    <t>Rouget de Lisle; Marseillaise; Hymne national; 1792</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Symboles de la République 📖 Glossaire - La Marseillaise</t>
+  </si>
+  <si>
+    <t>NAT-T4-050</t>
+  </si>
+  <si>
+    <t>Pour quel événement la tour Eiffel a-t-elle été construite en 1889 ?</t>
+  </si>
+  <si>
+    <t>Les Jeux olympiques.</t>
+  </si>
+  <si>
+    <t>L'Exposition universelle.</t>
+  </si>
+  <si>
+    <t>La Tour Eiffel, inaugurée en 1889, est construite pour l'Exposition universelle organisée à Paris à l'occasion du centenaire de la Révolution française.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : tour Eiffel (1889) = Exposition universelle</t>
+  </si>
+  <si>
+    <t>Connaître les grands monuments français.</t>
+  </si>
+  <si>
+    <t>Tour Eiffel; 1889; Exposition universelle; Paris</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Patrimoine 📖 Glossaire - Tour Eiffel</t>
+  </si>
+  <si>
+    <t>NAT-T4-051</t>
+  </si>
+  <si>
+    <t>Quelle chaîne de montagnes forme une frontière naturelle entre la France et l'Italie et abrite le Mont Blanc ?</t>
+  </si>
+  <si>
+    <t>Les Alpes forment une frontière naturelle entre la France et l'Italie. Elles abritent le Mont Blanc, point culminant de la France.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : frontière France-Italie = les Alpes (Mont Blanc)</t>
+  </si>
+  <si>
+    <t>Alpes; Italie; Montagnes; Mont Blanc</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Alpes</t>
+  </si>
+  <si>
+    <t>NAT-T4-052</t>
+  </si>
+  <si>
+    <t>Qui était Molière ?</t>
+  </si>
+  <si>
+    <t>Un peintre.</t>
+  </si>
+  <si>
+    <t>Un roi.</t>
+  </si>
+  <si>
+    <t>Un scientifique.</t>
+  </si>
+  <si>
+    <t>Un dramaturge et comédien français.</t>
+  </si>
+  <si>
+    <t>Molière (Jean-Baptiste Poquelin) est l'auteur de nombreuses comédies célèbres comme Le Misanthrope, L'Avare ou Le Bourgeois gentilhomme.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Molière = dramaturge et comédien français</t>
+  </si>
+  <si>
+    <t>Molière; Théâtre; Dramaturge</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Littérature 📖 Glossaire - Molière</t>
+  </si>
+  <si>
+    <t>NAT-T4-053</t>
+  </si>
+  <si>
+    <t>Qui était Charles Baudelaire, auteur des Fleurs du mal ?</t>
+  </si>
+  <si>
+    <t>Un musicien.</t>
+  </si>
+  <si>
+    <t>Un homme politique.</t>
+  </si>
+  <si>
+    <t>Un poète français.</t>
+  </si>
+  <si>
+    <t>Charles Baudelaire est l'un des plus grands poètes français du XIXᵉ siècle. Son œuvre la plus célèbre est Les Fleurs du mal.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Baudelaire = poète français (Les Fleurs du mal)</t>
+  </si>
+  <si>
+    <t>Baudelaire; Poésie; Les Fleurs du mal</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Littérature 📖 Glossaire - Charles Baudelaire</t>
+  </si>
+  <si>
+    <t>NAT-T4-054</t>
+  </si>
+  <si>
+    <t>Qui était George Sand ?</t>
+  </si>
+  <si>
+    <t>Une scientifique.</t>
+  </si>
+  <si>
+    <t>Une reine.</t>
+  </si>
+  <si>
+    <t>Une écrivaine française.</t>
+  </si>
+  <si>
+    <t>George Sand, de son vrai nom Aurore Dupin, est une grande romancière française du XIXᵉ siècle. Elle est connue pour son engagement en faveur de la liberté et de l'égalité.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : George Sand = écrivaine française (XIXe siècle)</t>
+  </si>
+  <si>
+    <t>George Sand; Romancière; Littérature</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Littérature 📖 Glossaire - George Sand</t>
+  </si>
+  <si>
+    <t>NAT-T4-055</t>
+  </si>
+  <si>
+    <t>Qui était Simone de Beauvoir, autrice du Deuxième Sexe ?</t>
+  </si>
+  <si>
+    <t>Une philosophe et écrivaine française.</t>
+  </si>
+  <si>
+    <t>Simone de Beauvoir est une philosophe, écrivaine et essayiste française. Son ouvrage Le Deuxième Sexe est une référence majeure dans l'histoire du féminisme.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Simone de Beauvoir = philosophe et écrivaine (Le Deuxième Sexe)</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures de la culture française.</t>
+  </si>
+  <si>
+    <t>Simone de Beauvoir; Philosophie; Féminisme; Le Deuxième Sexe</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Culture 📖 Glossaire - Simone de Beauvoir</t>
+  </si>
+  <si>
+    <t>NAT-T4-056</t>
+  </si>
+  <si>
+    <t>Qui était Albert Camus, prix Nobel de littérature en 1957 ?</t>
+  </si>
+  <si>
+    <t>Un compositeur.</t>
+  </si>
+  <si>
+    <t>Un écrivain et philosophe français.</t>
+  </si>
+  <si>
+    <t>Albert Camus est l'un des plus grands écrivains français du XXᵉ siècle. Il est notamment l'auteur de L'Étranger et La Peste et reçoit le prix Nobel de littérature en 1957.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Albert Camus = écrivain et philosophe, prix Nobel 1957</t>
+  </si>
+  <si>
+    <t>Albert Camus; Prix Nobel; L'Étranger; La Peste</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Littérature 📖 Glossaire - Albert Camus</t>
+  </si>
+  <si>
+    <t>NAT-T4-057</t>
+  </si>
+  <si>
+    <t>Qui était Marguerite Yourcenar, première femme élue à l'Académie française en 1980 ?</t>
+  </si>
+  <si>
+    <t>Une actrice.</t>
+  </si>
+  <si>
+    <t>Marguerite Yourcenar est une grande écrivaine française. En 1980, elle devient la première femme élue à l'Académie française.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Marguerite Yourcenar = 1ère femme à l'Académie française (1980)</t>
+  </si>
+  <si>
+    <t>Marguerite Yourcenar; Académie française; Écrivaine</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Littérature 📖 Glossaire - Académie française</t>
+  </si>
+  <si>
+    <t>NAT-T4-058</t>
+  </si>
+  <si>
+    <t>Qui était Paul Cézanne ?</t>
+  </si>
+  <si>
+    <t>Un écrivain.</t>
+  </si>
+  <si>
+    <t>Un sculpteur.</t>
+  </si>
+  <si>
+    <t>Un peintre français.</t>
+  </si>
+  <si>
+    <t>Paul Cézanne est un peintre français majeur de la fin du XIXᵉ siècle. Son œuvre a profondément influencé l'art moderne.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Paul Cézanne = peintre français</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures des arts.</t>
+  </si>
+  <si>
+    <t>Paul Cézanne; Peinture; Art</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Arts 📖 Glossaire - Paul Cézanne</t>
+  </si>
+  <si>
+    <t>NAT-T4-059</t>
+  </si>
+  <si>
+    <t>Qui est l'auteur de la célèbre sculpture Le Penseur ?</t>
+  </si>
+  <si>
+    <t>Un sculpteur français (Auguste Rodin).</t>
+  </si>
+  <si>
+    <t>Auguste Rodin est considéré comme le père de la sculpture moderne. Parmi ses œuvres les plus célèbres figurent Le Penseur et La Porte de l'Enfer.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Le Penseur = Auguste Rodin</t>
+  </si>
+  <si>
+    <t>Rodin; Sculpture; Le Penseur</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Arts 📖 Glossaire - Auguste Rodin</t>
+  </si>
+  <si>
+    <t>NAT-T4-060</t>
+  </si>
+  <si>
+    <t>Lequel de ces compositeurs est français ?</t>
+  </si>
+  <si>
+    <t>Claude Debussy.</t>
+  </si>
+  <si>
+    <t>La France compte de nombreux compositeurs mondialement connus, comme Claude Debussy, Maurice Ravel ou Georges Bizet, dont les œuvres sont jouées dans le monde entier.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : compositeurs français = Debussy, Ravel, Bizet...</t>
+  </si>
+  <si>
+    <t>Connaître les grandes figures de la musique française.</t>
+  </si>
+  <si>
+    <t>Debussy; Ravel; Bizet; Musique</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Musique 📖 Glossaire - Compositeur</t>
+  </si>
+  <si>
+    <t>NAT-T4-066</t>
+  </si>
+  <si>
+    <t>Quelle île française, collectivité territoriale unique, est située en Méditerranée ?</t>
+  </si>
+  <si>
+    <t>La Sardaigne.</t>
+  </si>
+  <si>
+    <t>La Sicile.</t>
+  </si>
+  <si>
+    <t>Majorque.</t>
+  </si>
+  <si>
+    <t>La Corse.</t>
+  </si>
+  <si>
+    <t>La Corse est une île française située en Méditerranée. Elle constitue une collectivité territoriale unique et fait partie intégrante de la République française.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : île française méditerranéenne = la Corse</t>
+  </si>
+  <si>
+    <t>Corse; Méditerranée; Île</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Corse</t>
+  </si>
+  <si>
+    <t>NAT-T4-067</t>
+  </si>
+  <si>
+    <t>Quel est le plus haut sommet de France, situé dans les Alpes ?</t>
+  </si>
+  <si>
+    <t>Le Canigou.</t>
+  </si>
+  <si>
+    <t>Le Puy de Dôme.</t>
+  </si>
+  <si>
+    <t>Le mont Ventoux.</t>
+  </si>
+  <si>
+    <t>Le Mont Blanc.</t>
+  </si>
+  <si>
+    <t>Le Mont Blanc, situé dans les Alpes, culmine à environ 4 805 mètres. Il est le plus haut sommet de France et d'Europe occidentale.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : plus haut sommet de France = Mont Blanc</t>
+  </si>
+  <si>
+    <t>Connaître le relief français.</t>
+  </si>
+  <si>
+    <t>Mont Blanc; Alpes; Montagne</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Mont Blanc</t>
+  </si>
+  <si>
+    <t>NAT-T4-068</t>
+  </si>
+  <si>
+    <t>Quel département français d'outre-mer est situé dans l'océan Indien, à l'est de Madagascar ?</t>
+  </si>
+  <si>
+    <t>La Martinique.</t>
+  </si>
+  <si>
+    <t>La Guadeloupe.</t>
+  </si>
+  <si>
+    <t>La Réunion.</t>
+  </si>
+  <si>
+    <t>La Réunion est un département et une région d'outre-mer situés dans l'océan Indien, à l'est de Madagascar.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : océan Indien (est de Madagascar) = La Réunion</t>
+  </si>
+  <si>
+    <t>Connaître la géographie de l'outre-mer.</t>
+  </si>
+  <si>
+    <t>Réunion; Océan Indien; Outre-mer</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - La Réunion</t>
+  </si>
+  <si>
+    <t>NAT-T4-069</t>
+  </si>
+  <si>
+    <t>Quel département français d'outre-mer se situe en Amérique du Sud, à la frontière du Brésil ?</t>
+  </si>
+  <si>
+    <t>Guadeloupe.</t>
+  </si>
+  <si>
+    <t>Martinique.</t>
+  </si>
+  <si>
+    <t>La Guyane.</t>
+  </si>
+  <si>
+    <t>La Guyane est un département et une région d'outre-mer d'Amérique du Sud. Elle partage une frontière avec le Brésil et le Suriname.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : frontière avec le Brésil = la Guyane</t>
+  </si>
+  <si>
+    <t>Guyane; Brésil; Outre-mer</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Guyane</t>
+  </si>
+  <si>
+    <t>NAT-T4-070</t>
+  </si>
+  <si>
+    <t>D'où décollent les fusées Ariane, au sein du Centre spatial guyanais ?</t>
+  </si>
+  <si>
+    <t>Toulouse.</t>
+  </si>
+  <si>
+    <t>Kourou.</t>
+  </si>
+  <si>
+    <t>Le Centre spatial guyanais, situé à Kourou, est le principal site de lancement spatial européen. Sa proximité avec l'équateur facilite les lancements de satellites.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : fusées Ariane = Kourou (Guyane)</t>
+  </si>
+  <si>
+    <t>Connaître les grands équipements français.</t>
+  </si>
+  <si>
+    <t>Kourou; Guyane; Ariane; Centre spatial guyanais</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Kourou - Centre spatial guyanais</t>
+  </si>
+  <si>
+    <t>NAT-T4-071</t>
+  </si>
+  <si>
+    <t>Laquelle de ces mers ou de ces océans borde la France métropolitaine ?</t>
+  </si>
+  <si>
+    <t>L'océan Pacifique.</t>
+  </si>
+  <si>
+    <t>La mer Noire.</t>
+  </si>
+  <si>
+    <t>La mer Rouge.</t>
+  </si>
+  <si>
+    <t>La France métropolitaine est bordée par la Manche, l'océan Atlantique et la mer Méditerranée. Une petite partie du littoral touche également la mer du Nord.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : littoral France métropolitaine = Manche, Atlantique, Méditerranée</t>
+  </si>
+  <si>
+    <t>Connaître la géographie physique de la France.</t>
+  </si>
+  <si>
+    <t>Atlantique; Manche; Méditerranée; Littoral</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Littoral</t>
+  </si>
+  <si>
+    <t>NAT-T4-072</t>
+  </si>
+  <si>
+    <t>Lequel de ces territoires est un département-région d'outre-mer insulaire français ?</t>
+  </si>
+  <si>
+    <t>La Nouvelle-Calédonie.</t>
+  </si>
+  <si>
+    <t>La Polynésie française.</t>
+  </si>
+  <si>
+    <t>Les îles françaises ayant le statut de département (ou département-région) d'outre-mer sont la Guadeloupe, la Martinique, La Réunion et Mayotte.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : DROM insulaires = Guadeloupe, Martinique, Réunion, Mayotte</t>
+  </si>
+  <si>
+    <t>Outre-mer; DROM; Réunion; Guadeloupe; Martinique; Mayotte</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - DROM</t>
+  </si>
+  <si>
+    <t>NAT-T4-073</t>
+  </si>
+  <si>
+    <t>Qu'appelle-t-on la « France d'outre-mer » ?</t>
+  </si>
+  <si>
+    <t>Les pays voisins de la France.</t>
+  </si>
+  <si>
+    <t>Les anciennes colonies françaises.</t>
+  </si>
+  <si>
+    <t>Les régions métropolitaines.</t>
+  </si>
+  <si>
+    <t>Les territoires français situés en dehors de l'Europe.</t>
+  </si>
+  <si>
+    <t>La France d'outre-mer regroupe les territoires français situés hors du continent européen. Ils possèdent des statuts différents (DROM, COM, etc.) mais appartiennent à la République française.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : France d'outre-mer = territoires hors d'Europe</t>
+  </si>
+  <si>
+    <t>Comprendre l'organisation territoriale française.</t>
+  </si>
+  <si>
+    <t>Outre-mer; DROM; COM; Territoires</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Outre-mer</t>
+  </si>
+  <si>
+    <t>NAT-T4-074</t>
+  </si>
+  <si>
+    <t>Quelle est, environ, la population de la France en 2025 ?</t>
+  </si>
+  <si>
+    <t>50 millions.</t>
+  </si>
+  <si>
+    <t>80 millions.</t>
+  </si>
+  <si>
+    <t>100 millions.</t>
+  </si>
+  <si>
+    <t>Environ 68 millions d'habitants.</t>
+  </si>
+  <si>
+    <t>En 2025, la France compte environ 68 millions d'habitants (France entière). L'objectif est de connaître un ordre de grandeur, pas un chiffre exact.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : population France (2025) = environ 68 millions</t>
+  </si>
+  <si>
+    <t>Connaître les grands repères démographiques.</t>
+  </si>
+  <si>
+    <t>Population; 68 millions; France</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Démographie</t>
+  </si>
+  <si>
+    <t>NAT-T4-075</t>
+  </si>
+  <si>
+    <t>Quel est le premier port français, aussi l'un des principaux ports de la Méditerranée ?</t>
+  </si>
+  <si>
+    <t>Le Grand Port Maritime de Marseille est le premier port français et l'un des principaux ports de la Méditerranée. Il joue un rôle essentiel dans le commerce et les échanges internationaux.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : premier port français = Marseille</t>
+  </si>
+  <si>
+    <t>Connaître les grands équipements économiques de la France.</t>
+  </si>
+  <si>
+    <t>Marseille; Port; Méditerranée; Commerce</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie économique 📖 Glossaire - Grand port maritime</t>
+  </si>
+  <si>
+    <t>NAT-T4-076</t>
+  </si>
+  <si>
+    <t>Combien de régions compte la France métropolitaine depuis la réforme territoriale de 2016 ?</t>
+  </si>
+  <si>
+    <t>18.</t>
+  </si>
+  <si>
+    <t>22.</t>
+  </si>
+  <si>
+    <t>Depuis la réforme territoriale de 2016, la France métropolitaine compte 13 régions. Si l'on ajoute les régions d'outre-mer, la France compte 18 régions au total.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : France métropolitaine (depuis 2016) = 13 régions</t>
+  </si>
+  <si>
+    <t>Connaître l'organisation territoriale française.</t>
+  </si>
+  <si>
+    <t>Régions; 13 régions; Réforme territoriale</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Région</t>
+  </si>
+  <si>
+    <t>NAT-T4-077</t>
+  </si>
+  <si>
+    <t>Quel département d'outre-mer se situe dans l'océan Indien, au sud-est du continent africain ?</t>
+  </si>
+  <si>
+    <t>La Réunion est un département et une région d'outre-mer français situé dans l'océan Indien, à l'est de Madagascar.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : océan Indien (sud-est de l'Afrique) = La Réunion</t>
+  </si>
+  <si>
+    <t>Réunion; Océan Indien; Afrique; Outre-mer</t>
+  </si>
+  <si>
+    <t>NAT-T4-078</t>
+  </si>
+  <si>
+    <t>Quel est le chef-lieu de la région Auvergne-Rhône-Alpes ?</t>
+  </si>
+  <si>
+    <t>Clermont-Ferrand.</t>
+  </si>
+  <si>
+    <t>Grenoble.</t>
+  </si>
+  <si>
+    <t>Saint-Étienne.</t>
+  </si>
+  <si>
+    <t>Lyon.</t>
+  </si>
+  <si>
+    <t>Lyon est le chef-lieu de la région Auvergne-Rhône-Alpes. C'est également la troisième commune la plus peuplée de France.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Auvergne-Rhône-Alpes = chef-lieu Lyon</t>
+  </si>
+  <si>
+    <t>Connaître les principales régions françaises.</t>
+  </si>
+  <si>
+    <t>Lyon; Auvergne-Rhône-Alpes; Chef-lieu</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Chef-lieu</t>
+  </si>
+  <si>
+    <t>NAT-T4-079</t>
+  </si>
+  <si>
+    <t>Quel est le chef-lieu de la région Bretagne ?</t>
+  </si>
+  <si>
+    <t>Brest.</t>
+  </si>
+  <si>
+    <t>Quimper.</t>
+  </si>
+  <si>
+    <t>Rennes.</t>
+  </si>
+  <si>
+    <t>Rennes est le chef-lieu de la région Bretagne. C'est également une grande ville universitaire et économique de l'ouest de la France.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : Bretagne = chef-lieu Rennes</t>
+  </si>
+  <si>
+    <t>Rennes; Bretagne; Chef-lieu</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Bretagne</t>
+  </si>
+  <si>
+    <t>NAT-T4-080</t>
+  </si>
+  <si>
+    <t>Quel est le chef-lieu de la région Provence-Alpes-Côte d'Azur ?</t>
+  </si>
+  <si>
+    <t>Nice.</t>
+  </si>
+  <si>
+    <t>Toulon.</t>
+  </si>
+  <si>
+    <t>Aix-en-Provence.</t>
+  </si>
+  <si>
+    <t>Marseille est le chef-lieu de la région Provence-Alpes-Côte d'Azur (PACA). C'est également la deuxième ville la plus peuplée de France et le premier port maritime du pays.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : PACA = chef-lieu Marseille</t>
+  </si>
+  <si>
+    <t>Marseille; PACA; Chef-lieu</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Provence-Alpes-Côte d'Azur</t>
+  </si>
+  <si>
+    <t>NAT-T4-081</t>
+  </si>
+  <si>
+    <t>Depuis 2011, quel territoire est devenu le 101ᵉ département français ?</t>
+  </si>
+  <si>
+    <t>Mayotte.</t>
+  </si>
+  <si>
+    <t>Depuis le 31 mars 2011, Mayotte est devenue le 101ᵉ département français. Elle est également une région d'outre-mer située dans l'océan Indien.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : 101e département (2011) = Mayotte</t>
+  </si>
+  <si>
+    <t>Mayotte; 101e département; Outre-mer</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Mayotte</t>
+  </si>
+  <si>
+    <t>NAT-T4-082</t>
+  </si>
+  <si>
+    <t>Dans quelle région se trouvent la plupart des grandes stations de ski françaises (Chamonix, Les Trois Vallées...) ?</t>
+  </si>
+  <si>
+    <t>Île-de-France.</t>
+  </si>
+  <si>
+    <t>Auvergne-Rhône-Alpes.</t>
+  </si>
+  <si>
+    <t>La région Auvergne-Rhône-Alpes accueille certaines des plus grandes stations de ski françaises, comme Chamonix, Les Trois Vallées, La Plagne ou Les Arcs.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : grandes stations de ski = Auvergne-Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>Auvergne-Rhône-Alpes; Alpes; Stations de ski</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Auvergne-Rhône-Alpes</t>
+  </si>
+  <si>
+    <t>NAT-T4-083</t>
+  </si>
+  <si>
+    <t>Quel fleuve traverse Paris avant de se jeter dans la Manche au Havre ?</t>
+  </si>
+  <si>
+    <t>Le Rhône.</t>
+  </si>
+  <si>
+    <t>La Loire.</t>
+  </si>
+  <si>
+    <t>La Garonne.</t>
+  </si>
+  <si>
+    <t>La Seine.</t>
+  </si>
+  <si>
+    <t>La Seine traverse Paris avant de se jeter dans la Manche au Havre. Les quais de Seine sont inscrits au patrimoine mondial de l'UNESCO.</t>
+  </si>
+  <si>
+    <t>Retenez le mot-clé : fleuve de Paris = la Seine</t>
+  </si>
+  <si>
+    <t>Seine; Paris; Fleuve; UNESCO</t>
+  </si>
+  <si>
+    <t>📚 Thématique 4 – Géographie 📖 Glossaire - Seine</t>
   </si>
 </sst>
 </file>
@@ -4421,7 +6635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W130"/>
+  <dimension ref="A1:W208"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -13674,6 +15888,5544 @@
         <v>68</v>
       </c>
     </row>
+    <row r="131" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>1343</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C131" s="3">
+        <v>4</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>1346</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>1347</v>
+      </c>
+      <c r="H131" s="2" t="s">
+        <v>1348</v>
+      </c>
+      <c r="I131" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="J131" s="2" t="s">
+        <v>1081</v>
+      </c>
+      <c r="K131" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="L131" s="2" t="s">
+        <v>1349</v>
+      </c>
+      <c r="M131" s="2" t="s">
+        <v>1350</v>
+      </c>
+      <c r="N131" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O131" s="2" t="s">
+        <v>1351</v>
+      </c>
+      <c r="P131" s="2" t="s">
+        <v>1352</v>
+      </c>
+      <c r="Q131" s="2" t="s">
+        <v>1353</v>
+      </c>
+      <c r="R131" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S131" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T131" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U131" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V131" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W131" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="132" spans="1:23" ht="105" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>1355</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C132" s="3">
+        <v>4</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>1356</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H132" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="I132" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="J132" s="2" t="s">
+        <v>1360</v>
+      </c>
+      <c r="K132" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L132" s="2" t="s">
+        <v>1361</v>
+      </c>
+      <c r="M132" s="2" t="s">
+        <v>1362</v>
+      </c>
+      <c r="N132" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O132" s="2" t="s">
+        <v>1363</v>
+      </c>
+      <c r="P132" s="2" t="s">
+        <v>1364</v>
+      </c>
+      <c r="Q132" s="2" t="s">
+        <v>1365</v>
+      </c>
+      <c r="R132" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S132" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T132" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U132" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V132" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W132" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="133" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>1366</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C133" s="3">
+        <v>4</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>1367</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="H133" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="I133" s="2" t="s">
+        <v>1370</v>
+      </c>
+      <c r="J133" s="2" t="s">
+        <v>1371</v>
+      </c>
+      <c r="K133" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L133" s="2" t="s">
+        <v>1372</v>
+      </c>
+      <c r="M133" s="2" t="s">
+        <v>1373</v>
+      </c>
+      <c r="N133" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O133" s="2" t="s">
+        <v>1374</v>
+      </c>
+      <c r="P133" s="2" t="s">
+        <v>1375</v>
+      </c>
+      <c r="Q133" s="2" t="s">
+        <v>1376</v>
+      </c>
+      <c r="R133" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S133" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T133" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U133" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V133" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W133" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="134" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C134" s="3">
+        <v>4</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>1379</v>
+      </c>
+      <c r="H134" s="2" t="s">
+        <v>1380</v>
+      </c>
+      <c r="I134" s="2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="J134" s="2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="K134" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L134" s="2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="M134" s="2" t="s">
+        <v>1384</v>
+      </c>
+      <c r="N134" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O134" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="P134" s="2" t="s">
+        <v>1386</v>
+      </c>
+      <c r="Q134" s="2" t="s">
+        <v>1387</v>
+      </c>
+      <c r="R134" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S134" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T134" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U134" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V134" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W134" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="135" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C135" s="3">
+        <v>4</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>1389</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>1390</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>1391</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>1392</v>
+      </c>
+      <c r="J135" s="2" t="s">
+        <v>1393</v>
+      </c>
+      <c r="K135" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L135" s="2" t="s">
+        <v>1394</v>
+      </c>
+      <c r="M135" s="2" t="s">
+        <v>1395</v>
+      </c>
+      <c r="N135" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O135" s="2" t="s">
+        <v>1396</v>
+      </c>
+      <c r="P135" s="2" t="s">
+        <v>1397</v>
+      </c>
+      <c r="Q135" s="2" t="s">
+        <v>1398</v>
+      </c>
+      <c r="R135" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S135" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T135" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U135" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V135" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W135" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="136" spans="1:23" ht="90" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>1399</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C136" s="3">
+        <v>4</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>1401</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>1402</v>
+      </c>
+      <c r="J136" s="2" t="s">
+        <v>1403</v>
+      </c>
+      <c r="K136" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L136" s="2" t="s">
+        <v>1404</v>
+      </c>
+      <c r="M136" s="2" t="s">
+        <v>1405</v>
+      </c>
+      <c r="N136" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O136" s="2" t="s">
+        <v>1406</v>
+      </c>
+      <c r="P136" s="2" t="s">
+        <v>1407</v>
+      </c>
+      <c r="Q136" s="2" t="s">
+        <v>1408</v>
+      </c>
+      <c r="R136" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S136" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T136" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U136" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V136" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W136" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="137" spans="1:23" ht="90" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>1409</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C137" s="3">
+        <v>4</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>1411</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H137" s="2" t="s">
+        <v>1413</v>
+      </c>
+      <c r="I137" s="2" t="s">
+        <v>1414</v>
+      </c>
+      <c r="J137" s="2" t="s">
+        <v>1415</v>
+      </c>
+      <c r="K137" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L137" s="2" t="s">
+        <v>1416</v>
+      </c>
+      <c r="M137" s="2" t="s">
+        <v>1417</v>
+      </c>
+      <c r="N137" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O137" s="2" t="s">
+        <v>1418</v>
+      </c>
+      <c r="P137" s="2" t="s">
+        <v>1419</v>
+      </c>
+      <c r="Q137" s="2" t="s">
+        <v>1420</v>
+      </c>
+      <c r="R137" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S137" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T137" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U137" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V137" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W137" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="138" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>1421</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C138" s="3">
+        <v>4</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>1422</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="H138" s="2" t="s">
+        <v>1424</v>
+      </c>
+      <c r="I138" s="2" t="s">
+        <v>1425</v>
+      </c>
+      <c r="J138" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="K138" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L138" s="2" t="s">
+        <v>1427</v>
+      </c>
+      <c r="M138" s="2" t="s">
+        <v>1428</v>
+      </c>
+      <c r="N138" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O138" s="2" t="s">
+        <v>1429</v>
+      </c>
+      <c r="P138" s="2" t="s">
+        <v>1430</v>
+      </c>
+      <c r="Q138" s="2" t="s">
+        <v>1431</v>
+      </c>
+      <c r="R138" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S138" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T138" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U138" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V138" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W138" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="139" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>1432</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C139" s="3">
+        <v>4</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>1433</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H139" s="2" t="s">
+        <v>1435</v>
+      </c>
+      <c r="I139" s="2" t="s">
+        <v>1436</v>
+      </c>
+      <c r="J139" s="2" t="s">
+        <v>1437</v>
+      </c>
+      <c r="K139" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L139" s="2" t="s">
+        <v>1438</v>
+      </c>
+      <c r="M139" s="2" t="s">
+        <v>1439</v>
+      </c>
+      <c r="N139" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O139" s="2" t="s">
+        <v>1440</v>
+      </c>
+      <c r="P139" s="2" t="s">
+        <v>1441</v>
+      </c>
+      <c r="Q139" s="2" t="s">
+        <v>1442</v>
+      </c>
+      <c r="R139" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S139" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T139" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U139" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V139" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W139" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="140" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>1443</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C140" s="3">
+        <v>4</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>1444</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H140" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="I140" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="J140" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="K140" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L140" s="2" t="s">
+        <v>1447</v>
+      </c>
+      <c r="M140" s="2" t="s">
+        <v>1448</v>
+      </c>
+      <c r="N140" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O140" s="2" t="s">
+        <v>1385</v>
+      </c>
+      <c r="P140" s="2" t="s">
+        <v>1449</v>
+      </c>
+      <c r="Q140" s="2" t="s">
+        <v>1450</v>
+      </c>
+      <c r="R140" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S140" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T140" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U140" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V140" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W140" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="141" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>1451</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" s="3">
+        <v>4</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>1452</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="H141" s="2" t="s">
+        <v>1453</v>
+      </c>
+      <c r="I141" s="2" t="s">
+        <v>1454</v>
+      </c>
+      <c r="J141" s="2" t="s">
+        <v>1455</v>
+      </c>
+      <c r="K141" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L141" s="2" t="s">
+        <v>1456</v>
+      </c>
+      <c r="M141" s="2" t="s">
+        <v>1457</v>
+      </c>
+      <c r="N141" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O141" s="2" t="s">
+        <v>1458</v>
+      </c>
+      <c r="P141" s="2" t="s">
+        <v>1459</v>
+      </c>
+      <c r="Q141" s="2" t="s">
+        <v>1460</v>
+      </c>
+      <c r="R141" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S141" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T141" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U141" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V141" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W141" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="142" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>1461</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C142" s="3">
+        <v>4</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>1462</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>1463</v>
+      </c>
+      <c r="H142" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="I142" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="J142" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="K142" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L142" s="2" t="s">
+        <v>1466</v>
+      </c>
+      <c r="M142" s="2" t="s">
+        <v>1467</v>
+      </c>
+      <c r="N142" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="O142" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="P142" s="2" t="s">
+        <v>1469</v>
+      </c>
+      <c r="Q142" s="2" t="s">
+        <v>1470</v>
+      </c>
+      <c r="R142" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S142" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T142" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U142" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V142" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W142" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="143" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>1471</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C143" s="3">
+        <v>4</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>1472</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H143" s="2" t="s">
+        <v>1473</v>
+      </c>
+      <c r="I143" s="2" t="s">
+        <v>1465</v>
+      </c>
+      <c r="J143" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="K143" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L143" s="2" t="s">
+        <v>1474</v>
+      </c>
+      <c r="M143" s="2" t="s">
+        <v>1475</v>
+      </c>
+      <c r="N143" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O143" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="P143" s="2" t="s">
+        <v>1476</v>
+      </c>
+      <c r="Q143" s="2" t="s">
+        <v>1477</v>
+      </c>
+      <c r="R143" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S143" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T143" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U143" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V143" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W143" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="144" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>1478</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C144" s="3">
+        <v>4</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>1479</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="H144" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="I144" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="J144" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="K144" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="L144" s="2" t="s">
+        <v>1480</v>
+      </c>
+      <c r="M144" s="2" t="s">
+        <v>1481</v>
+      </c>
+      <c r="N144" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O144" s="2" t="s">
+        <v>1482</v>
+      </c>
+      <c r="P144" s="2" t="s">
+        <v>1483</v>
+      </c>
+      <c r="Q144" s="2" t="s">
+        <v>1484</v>
+      </c>
+      <c r="R144" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S144" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T144" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U144" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V144" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W144" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="145" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>1485</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C145" s="3">
+        <v>4</v>
+      </c>
+      <c r="D145" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E145" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>1486</v>
+      </c>
+      <c r="G145" s="2" t="s">
+        <v>1487</v>
+      </c>
+      <c r="H145" s="2" t="s">
+        <v>1488</v>
+      </c>
+      <c r="I145" s="2" t="s">
+        <v>1489</v>
+      </c>
+      <c r="J145" s="2" t="s">
+        <v>1490</v>
+      </c>
+      <c r="K145" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L145" s="2" t="s">
+        <v>1491</v>
+      </c>
+      <c r="M145" s="2" t="s">
+        <v>1492</v>
+      </c>
+      <c r="N145" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O145" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="P145" s="2" t="s">
+        <v>1494</v>
+      </c>
+      <c r="Q145" s="2" t="s">
+        <v>1495</v>
+      </c>
+      <c r="R145" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S145" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T145" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U145" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V145" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W145" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="146" spans="1:23" ht="90" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C146" s="3">
+        <v>4</v>
+      </c>
+      <c r="D146" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E146" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>1497</v>
+      </c>
+      <c r="G146" s="2" t="s">
+        <v>1498</v>
+      </c>
+      <c r="H146" s="2" t="s">
+        <v>981</v>
+      </c>
+      <c r="I146" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="J146" s="2" t="s">
+        <v>1500</v>
+      </c>
+      <c r="K146" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L146" s="2" t="s">
+        <v>1501</v>
+      </c>
+      <c r="M146" s="2" t="s">
+        <v>1502</v>
+      </c>
+      <c r="N146" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O146" s="2" t="s">
+        <v>1503</v>
+      </c>
+      <c r="P146" s="2" t="s">
+        <v>1504</v>
+      </c>
+      <c r="Q146" s="2" t="s">
+        <v>1505</v>
+      </c>
+      <c r="R146" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S146" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T146" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U146" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V146" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W146" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="147" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>1506</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C147" s="3">
+        <v>4</v>
+      </c>
+      <c r="D147" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E147" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>1508</v>
+      </c>
+      <c r="G147" s="2" t="s">
+        <v>1509</v>
+      </c>
+      <c r="H147" s="2" t="s">
+        <v>1510</v>
+      </c>
+      <c r="I147" s="2" t="s">
+        <v>1511</v>
+      </c>
+      <c r="J147" s="2" t="s">
+        <v>1512</v>
+      </c>
+      <c r="K147" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L147" s="2" t="s">
+        <v>1513</v>
+      </c>
+      <c r="M147" s="2" t="s">
+        <v>1514</v>
+      </c>
+      <c r="N147" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O147" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="P147" s="2" t="s">
+        <v>1516</v>
+      </c>
+      <c r="Q147" s="2" t="s">
+        <v>1517</v>
+      </c>
+      <c r="R147" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S147" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T147" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U147" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V147" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W147" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="148" spans="1:23" ht="105" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C148" s="3">
+        <v>4</v>
+      </c>
+      <c r="D148" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E148" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>1519</v>
+      </c>
+      <c r="G148" s="2" t="s">
+        <v>1412</v>
+      </c>
+      <c r="H148" s="2" t="s">
+        <v>1520</v>
+      </c>
+      <c r="I148" s="2" t="s">
+        <v>1521</v>
+      </c>
+      <c r="J148" s="2" t="s">
+        <v>1522</v>
+      </c>
+      <c r="K148" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L148" s="2" t="s">
+        <v>1523</v>
+      </c>
+      <c r="M148" s="2" t="s">
+        <v>1524</v>
+      </c>
+      <c r="N148" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O148" s="2" t="s">
+        <v>1525</v>
+      </c>
+      <c r="P148" s="2" t="s">
+        <v>1526</v>
+      </c>
+      <c r="Q148" s="2" t="s">
+        <v>1527</v>
+      </c>
+      <c r="R148" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S148" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T148" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U148" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V148" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W148" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="149" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C149" s="3">
+        <v>4</v>
+      </c>
+      <c r="D149" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E149" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F149" s="2" t="s">
+        <v>1529</v>
+      </c>
+      <c r="G149" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H149" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="I149" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="J149" s="2" t="s">
+        <v>1530</v>
+      </c>
+      <c r="K149" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L149" s="2" t="s">
+        <v>1531</v>
+      </c>
+      <c r="M149" s="2" t="s">
+        <v>1532</v>
+      </c>
+      <c r="N149" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O149" s="2" t="s">
+        <v>1533</v>
+      </c>
+      <c r="P149" s="2" t="s">
+        <v>1534</v>
+      </c>
+      <c r="Q149" s="2" t="s">
+        <v>1535</v>
+      </c>
+      <c r="R149" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S149" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T149" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U149" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V149" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W149" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="150" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
+        <v>1536</v>
+      </c>
+      <c r="B150" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C150" s="3">
+        <v>4</v>
+      </c>
+      <c r="D150" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E150" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F150" s="2" t="s">
+        <v>1537</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>815</v>
+      </c>
+      <c r="H150" s="2" t="s">
+        <v>816</v>
+      </c>
+      <c r="I150" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="J150" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="K150" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L150" s="2" t="s">
+        <v>1538</v>
+      </c>
+      <c r="M150" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="N150" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O150" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="P150" s="2" t="s">
+        <v>1539</v>
+      </c>
+      <c r="Q150" s="2" t="s">
+        <v>1540</v>
+      </c>
+      <c r="R150" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S150" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T150" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U150" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V150" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W150" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="151" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A151" s="2" t="s">
+        <v>1541</v>
+      </c>
+      <c r="B151" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C151" s="3">
+        <v>4</v>
+      </c>
+      <c r="D151" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E151" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F151" s="2" t="s">
+        <v>1542</v>
+      </c>
+      <c r="G151" s="2" t="s">
+        <v>1543</v>
+      </c>
+      <c r="H151" s="2" t="s">
+        <v>1544</v>
+      </c>
+      <c r="I151" s="2" t="s">
+        <v>1545</v>
+      </c>
+      <c r="J151" s="2" t="s">
+        <v>1546</v>
+      </c>
+      <c r="K151" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L151" s="2" t="s">
+        <v>1547</v>
+      </c>
+      <c r="M151" s="2" t="s">
+        <v>1548</v>
+      </c>
+      <c r="N151" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O151" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="P151" s="2" t="s">
+        <v>1550</v>
+      </c>
+      <c r="Q151" s="2" t="s">
+        <v>1551</v>
+      </c>
+      <c r="R151" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S151" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T151" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U151" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V151" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W151" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="152" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A152" s="2" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B152" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C152" s="3">
+        <v>4</v>
+      </c>
+      <c r="D152" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E152" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F152" s="2" t="s">
+        <v>1553</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>1554</v>
+      </c>
+      <c r="H152" s="2" t="s">
+        <v>1555</v>
+      </c>
+      <c r="I152" s="2" t="s">
+        <v>1556</v>
+      </c>
+      <c r="J152" s="2" t="s">
+        <v>1557</v>
+      </c>
+      <c r="K152" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L152" s="2" t="s">
+        <v>1558</v>
+      </c>
+      <c r="M152" s="2" t="s">
+        <v>1559</v>
+      </c>
+      <c r="N152" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O152" s="2" t="s">
+        <v>1549</v>
+      </c>
+      <c r="P152" s="2" t="s">
+        <v>1560</v>
+      </c>
+      <c r="Q152" s="2" t="s">
+        <v>1561</v>
+      </c>
+      <c r="R152" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S152" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T152" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U152" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V152" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W152" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="153" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A153" s="2" t="s">
+        <v>1562</v>
+      </c>
+      <c r="B153" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C153" s="3">
+        <v>4</v>
+      </c>
+      <c r="D153" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E153" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F153" s="2" t="s">
+        <v>1563</v>
+      </c>
+      <c r="G153" s="2" t="s">
+        <v>1446</v>
+      </c>
+      <c r="H153" s="2" t="s">
+        <v>1564</v>
+      </c>
+      <c r="I153" s="2" t="s">
+        <v>1565</v>
+      </c>
+      <c r="J153" s="2" t="s">
+        <v>1566</v>
+      </c>
+      <c r="K153" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L153" s="2" t="s">
+        <v>1567</v>
+      </c>
+      <c r="M153" s="2" t="s">
+        <v>1568</v>
+      </c>
+      <c r="N153" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O153" s="2" t="s">
+        <v>1569</v>
+      </c>
+      <c r="P153" s="2" t="s">
+        <v>1570</v>
+      </c>
+      <c r="Q153" s="2" t="s">
+        <v>1571</v>
+      </c>
+      <c r="R153" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S153" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T153" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U153" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V153" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W153" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="154" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A154" s="2" t="s">
+        <v>1572</v>
+      </c>
+      <c r="B154" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C154" s="3">
+        <v>4</v>
+      </c>
+      <c r="D154" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E154" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F154" s="2" t="s">
+        <v>1573</v>
+      </c>
+      <c r="G154" s="2" t="s">
+        <v>1574</v>
+      </c>
+      <c r="H154" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="I154" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="J154" s="2" t="s">
+        <v>1577</v>
+      </c>
+      <c r="K154" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L154" s="2" t="s">
+        <v>1578</v>
+      </c>
+      <c r="M154" s="2" t="s">
+        <v>1579</v>
+      </c>
+      <c r="N154" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O154" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P154" s="2" t="s">
+        <v>1580</v>
+      </c>
+      <c r="Q154" s="2" t="s">
+        <v>1581</v>
+      </c>
+      <c r="R154" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S154" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T154" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U154" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V154" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W154" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="155" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A155" s="2" t="s">
+        <v>1582</v>
+      </c>
+      <c r="B155" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C155" s="3">
+        <v>4</v>
+      </c>
+      <c r="D155" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E155" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F155" s="2" t="s">
+        <v>1583</v>
+      </c>
+      <c r="G155" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H155" s="2" t="s">
+        <v>912</v>
+      </c>
+      <c r="I155" s="2" t="s">
+        <v>1585</v>
+      </c>
+      <c r="J155" s="2" t="s">
+        <v>1586</v>
+      </c>
+      <c r="K155" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L155" s="2" t="s">
+        <v>1587</v>
+      </c>
+      <c r="M155" s="2" t="s">
+        <v>1588</v>
+      </c>
+      <c r="N155" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O155" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="P155" s="2" t="s">
+        <v>1589</v>
+      </c>
+      <c r="Q155" s="2" t="s">
+        <v>1590</v>
+      </c>
+      <c r="R155" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S155" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T155" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U155" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V155" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W155" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="156" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A156" s="2" t="s">
+        <v>1591</v>
+      </c>
+      <c r="B156" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C156" s="3">
+        <v>4</v>
+      </c>
+      <c r="D156" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E156" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F156" s="2" t="s">
+        <v>1592</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>1357</v>
+      </c>
+      <c r="H156" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="I156" s="2" t="s">
+        <v>1358</v>
+      </c>
+      <c r="J156" s="2" t="s">
+        <v>1593</v>
+      </c>
+      <c r="K156" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L156" s="2" t="s">
+        <v>1594</v>
+      </c>
+      <c r="M156" s="2" t="s">
+        <v>1595</v>
+      </c>
+      <c r="N156" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O156" s="2" t="s">
+        <v>1596</v>
+      </c>
+      <c r="P156" s="2" t="s">
+        <v>1597</v>
+      </c>
+      <c r="Q156" s="2" t="s">
+        <v>1598</v>
+      </c>
+      <c r="R156" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S156" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T156" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U156" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V156" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W156" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="157" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B157" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C157" s="3">
+        <v>4</v>
+      </c>
+      <c r="D157" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E157" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F157" s="2" t="s">
+        <v>1601</v>
+      </c>
+      <c r="G157" s="2" t="s">
+        <v>1602</v>
+      </c>
+      <c r="H157" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="I157" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="J157" s="2" t="s">
+        <v>1605</v>
+      </c>
+      <c r="K157" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L157" s="2" t="s">
+        <v>1606</v>
+      </c>
+      <c r="M157" s="2" t="s">
+        <v>1607</v>
+      </c>
+      <c r="N157" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O157" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P157" s="2" t="s">
+        <v>1609</v>
+      </c>
+      <c r="Q157" s="2" t="s">
+        <v>1610</v>
+      </c>
+      <c r="R157" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S157" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T157" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U157" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V157" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W157" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="158" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
+        <v>1611</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C158" s="3">
+        <v>4</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F158" s="2" t="s">
+        <v>1612</v>
+      </c>
+      <c r="G158" s="2" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H158" s="2" t="s">
+        <v>1613</v>
+      </c>
+      <c r="I158" s="2" t="s">
+        <v>1614</v>
+      </c>
+      <c r="J158" s="2" t="s">
+        <v>1615</v>
+      </c>
+      <c r="K158" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L158" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="M158" s="2" t="s">
+        <v>1617</v>
+      </c>
+      <c r="N158" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O158" s="2" t="s">
+        <v>1618</v>
+      </c>
+      <c r="P158" s="2" t="s">
+        <v>1619</v>
+      </c>
+      <c r="Q158" s="2" t="s">
+        <v>1620</v>
+      </c>
+      <c r="R158" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S158" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T158" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U158" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V158" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W158" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="159" spans="1:23" ht="30" x14ac:dyDescent="0.3">
+      <c r="A159" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="B159" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C159" s="3">
+        <v>4</v>
+      </c>
+      <c r="D159" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E159" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F159" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="H159" s="2" t="s">
+        <v>1464</v>
+      </c>
+      <c r="I159" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="J159" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="K159" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L159" s="2" t="s">
+        <v>1624</v>
+      </c>
+      <c r="M159" s="2" t="s">
+        <v>1625</v>
+      </c>
+      <c r="N159" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O159" s="2" t="s">
+        <v>1468</v>
+      </c>
+      <c r="P159" s="2" t="s">
+        <v>1626</v>
+      </c>
+      <c r="Q159" s="2" t="s">
+        <v>1627</v>
+      </c>
+      <c r="R159" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S159" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T159" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U159" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V159" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W159" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="160" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A160" s="2" t="s">
+        <v>1628</v>
+      </c>
+      <c r="B160" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C160" s="3">
+        <v>4</v>
+      </c>
+      <c r="D160" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E160" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F160" s="2" t="s">
+        <v>1629</v>
+      </c>
+      <c r="G160" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="H160" s="2" t="s">
+        <v>1359</v>
+      </c>
+      <c r="I160" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="J160" s="2" t="s">
+        <v>1630</v>
+      </c>
+      <c r="K160" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L160" s="2" t="s">
+        <v>1631</v>
+      </c>
+      <c r="M160" s="2" t="s">
+        <v>1632</v>
+      </c>
+      <c r="N160" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O160" s="2" t="s">
+        <v>1633</v>
+      </c>
+      <c r="P160" s="2" t="s">
+        <v>1634</v>
+      </c>
+      <c r="Q160" s="2" t="s">
+        <v>1635</v>
+      </c>
+      <c r="R160" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S160" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T160" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U160" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V160" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W160" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="161" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A161" s="2" t="s">
+        <v>1636</v>
+      </c>
+      <c r="B161" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C161" s="3">
+        <v>4</v>
+      </c>
+      <c r="D161" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E161" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F161" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="G161" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="H161" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="I161" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="J161" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="K161" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L161" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="M161" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="N161" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O161" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="P161" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="Q161" s="2" t="s">
+        <v>1644</v>
+      </c>
+      <c r="R161" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S161" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T161" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U161" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V161" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W161" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="162" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A162" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="B162" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C162" s="3">
+        <v>4</v>
+      </c>
+      <c r="D162" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E162" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F162" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="H162" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="I162" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="J162" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="K162" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L162" s="2" t="s">
+        <v>1651</v>
+      </c>
+      <c r="M162" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="N162" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O162" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P162" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="Q162" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="R162" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S162" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T162" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U162" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V162" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W162" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="163" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A163" s="2" t="s">
+        <v>1655</v>
+      </c>
+      <c r="B163" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C163" s="3">
+        <v>4</v>
+      </c>
+      <c r="D163" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E163" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F163" s="2" t="s">
+        <v>1656</v>
+      </c>
+      <c r="G163" s="2" t="s">
+        <v>1657</v>
+      </c>
+      <c r="H163" s="2" t="s">
+        <v>1658</v>
+      </c>
+      <c r="I163" s="2" t="s">
+        <v>1659</v>
+      </c>
+      <c r="J163" s="2" t="s">
+        <v>1660</v>
+      </c>
+      <c r="K163" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L163" s="2" t="s">
+        <v>1661</v>
+      </c>
+      <c r="M163" s="2" t="s">
+        <v>1662</v>
+      </c>
+      <c r="N163" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O163" s="2" t="s">
+        <v>1663</v>
+      </c>
+      <c r="P163" s="2" t="s">
+        <v>1664</v>
+      </c>
+      <c r="Q163" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="R163" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S163" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T163" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U163" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V163" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W163" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="164" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A164" s="2" t="s">
+        <v>1666</v>
+      </c>
+      <c r="B164" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C164" s="3">
+        <v>4</v>
+      </c>
+      <c r="D164" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E164" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F164" s="2" t="s">
+        <v>1667</v>
+      </c>
+      <c r="G164" s="2" t="s">
+        <v>1584</v>
+      </c>
+      <c r="H164" s="2" t="s">
+        <v>1668</v>
+      </c>
+      <c r="I164" s="2" t="s">
+        <v>1669</v>
+      </c>
+      <c r="J164" s="2" t="s">
+        <v>1670</v>
+      </c>
+      <c r="K164" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L164" s="2" t="s">
+        <v>1671</v>
+      </c>
+      <c r="M164" s="2" t="s">
+        <v>1672</v>
+      </c>
+      <c r="N164" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O164" s="2" t="s">
+        <v>1673</v>
+      </c>
+      <c r="P164" s="2" t="s">
+        <v>1674</v>
+      </c>
+      <c r="Q164" s="2" t="s">
+        <v>1675</v>
+      </c>
+      <c r="R164" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S164" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T164" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U164" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V164" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W164" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="165" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A165" s="2" t="s">
+        <v>1676</v>
+      </c>
+      <c r="B165" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C165" s="3">
+        <v>4</v>
+      </c>
+      <c r="D165" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E165" s="2" t="s">
+        <v>1410</v>
+      </c>
+      <c r="F165" s="2" t="s">
+        <v>1677</v>
+      </c>
+      <c r="G165" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="H165" s="2" t="s">
+        <v>1678</v>
+      </c>
+      <c r="I165" s="2" t="s">
+        <v>1679</v>
+      </c>
+      <c r="J165" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="K165" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L165" s="2" t="s">
+        <v>1680</v>
+      </c>
+      <c r="M165" s="2" t="s">
+        <v>1681</v>
+      </c>
+      <c r="N165" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O165" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="P165" s="2" t="s">
+        <v>1682</v>
+      </c>
+      <c r="Q165" s="2" t="s">
+        <v>1683</v>
+      </c>
+      <c r="R165" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S165" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T165" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U165" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V165" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W165" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="166" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A166" s="2" t="s">
+        <v>1684</v>
+      </c>
+      <c r="B166" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C166" s="3">
+        <v>4</v>
+      </c>
+      <c r="D166" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E166" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F166" s="2" t="s">
+        <v>1685</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>1686</v>
+      </c>
+      <c r="H166" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="I166" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="J166" s="2" t="s">
+        <v>1687</v>
+      </c>
+      <c r="K166" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L166" s="2" t="s">
+        <v>1688</v>
+      </c>
+      <c r="M166" s="2" t="s">
+        <v>1689</v>
+      </c>
+      <c r="N166" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O166" s="2" t="s">
+        <v>1493</v>
+      </c>
+      <c r="P166" s="2" t="s">
+        <v>1690</v>
+      </c>
+      <c r="Q166" s="2" t="s">
+        <v>1691</v>
+      </c>
+      <c r="R166" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S166" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T166" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U166" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V166" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W166" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="167" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A167" s="2" t="s">
+        <v>1692</v>
+      </c>
+      <c r="B167" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C167" s="3">
+        <v>4</v>
+      </c>
+      <c r="D167" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E167" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F167" s="2" t="s">
+        <v>1693</v>
+      </c>
+      <c r="G167" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="H167" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="I167" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="J167" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="K167" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L167" s="2" t="s">
+        <v>1698</v>
+      </c>
+      <c r="M167" s="2" t="s">
+        <v>1699</v>
+      </c>
+      <c r="N167" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O167" s="2" t="s">
+        <v>1700</v>
+      </c>
+      <c r="P167" s="2" t="s">
+        <v>1701</v>
+      </c>
+      <c r="Q167" s="2" t="s">
+        <v>1702</v>
+      </c>
+      <c r="R167" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S167" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T167" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U167" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V167" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W167" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="168" spans="1:23" ht="120" x14ac:dyDescent="0.3">
+      <c r="A168" s="2" t="s">
+        <v>1703</v>
+      </c>
+      <c r="B168" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C168" s="3">
+        <v>4</v>
+      </c>
+      <c r="D168" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E168" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F168" s="2" t="s">
+        <v>1704</v>
+      </c>
+      <c r="G168" s="2" t="s">
+        <v>1705</v>
+      </c>
+      <c r="H168" s="2" t="s">
+        <v>1706</v>
+      </c>
+      <c r="I168" s="2" t="s">
+        <v>1707</v>
+      </c>
+      <c r="J168" s="2" t="s">
+        <v>1708</v>
+      </c>
+      <c r="K168" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L168" s="2" t="s">
+        <v>1709</v>
+      </c>
+      <c r="M168" s="2" t="s">
+        <v>1710</v>
+      </c>
+      <c r="N168" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O168" s="2" t="s">
+        <v>1711</v>
+      </c>
+      <c r="P168" s="2" t="s">
+        <v>1712</v>
+      </c>
+      <c r="Q168" s="2" t="s">
+        <v>1713</v>
+      </c>
+      <c r="R168" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S168" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T168" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U168" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V168" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W168" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="169" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A169" s="2" t="s">
+        <v>1714</v>
+      </c>
+      <c r="B169" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C169" s="3">
+        <v>4</v>
+      </c>
+      <c r="D169" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E169" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F169" s="2" t="s">
+        <v>1715</v>
+      </c>
+      <c r="G169" s="2" t="s">
+        <v>1716</v>
+      </c>
+      <c r="H169" s="2" t="s">
+        <v>1717</v>
+      </c>
+      <c r="I169" s="2" t="s">
+        <v>1718</v>
+      </c>
+      <c r="J169" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="K169" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L169" s="2" t="s">
+        <v>1720</v>
+      </c>
+      <c r="M169" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="N169" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O169" s="2" t="s">
+        <v>1722</v>
+      </c>
+      <c r="P169" s="2" t="s">
+        <v>1723</v>
+      </c>
+      <c r="Q169" s="2" t="s">
+        <v>1724</v>
+      </c>
+      <c r="R169" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S169" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T169" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U169" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V169" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W169" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="170" spans="1:23" ht="90" x14ac:dyDescent="0.3">
+      <c r="A170" s="2" t="s">
+        <v>1725</v>
+      </c>
+      <c r="B170" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C170" s="3">
+        <v>4</v>
+      </c>
+      <c r="D170" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E170" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F170" s="2" t="s">
+        <v>1726</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>1727</v>
+      </c>
+      <c r="H170" s="2" t="s">
+        <v>1728</v>
+      </c>
+      <c r="I170" s="2" t="s">
+        <v>1729</v>
+      </c>
+      <c r="J170" s="2" t="s">
+        <v>1730</v>
+      </c>
+      <c r="K170" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L170" s="2" t="s">
+        <v>1731</v>
+      </c>
+      <c r="M170" s="2" t="s">
+        <v>1732</v>
+      </c>
+      <c r="N170" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O170" s="2" t="s">
+        <v>1733</v>
+      </c>
+      <c r="P170" s="2" t="s">
+        <v>1734</v>
+      </c>
+      <c r="Q170" s="2" t="s">
+        <v>1735</v>
+      </c>
+      <c r="R170" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S170" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T170" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U170" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V170" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W170" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="171" spans="1:23" ht="105" x14ac:dyDescent="0.3">
+      <c r="A171" s="2" t="s">
+        <v>1736</v>
+      </c>
+      <c r="B171" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C171" s="3">
+        <v>4</v>
+      </c>
+      <c r="D171" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E171" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F171" s="2" t="s">
+        <v>1737</v>
+      </c>
+      <c r="G171" s="2" t="s">
+        <v>1738</v>
+      </c>
+      <c r="H171" s="2" t="s">
+        <v>1739</v>
+      </c>
+      <c r="I171" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="J171" s="2" t="s">
+        <v>1741</v>
+      </c>
+      <c r="K171" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L171" s="2" t="s">
+        <v>1742</v>
+      </c>
+      <c r="M171" s="2" t="s">
+        <v>1743</v>
+      </c>
+      <c r="N171" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O171" s="2" t="s">
+        <v>1744</v>
+      </c>
+      <c r="P171" s="2" t="s">
+        <v>1745</v>
+      </c>
+      <c r="Q171" s="2" t="s">
+        <v>1746</v>
+      </c>
+      <c r="R171" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S171" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T171" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U171" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V171" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W171" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="172" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A172" s="2" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B172" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C172" s="3">
+        <v>4</v>
+      </c>
+      <c r="D172" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E172" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>1748</v>
+      </c>
+      <c r="G172" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="H172" s="2" t="s">
+        <v>1749</v>
+      </c>
+      <c r="I172" s="2" t="s">
+        <v>1750</v>
+      </c>
+      <c r="J172" s="2" t="s">
+        <v>1751</v>
+      </c>
+      <c r="K172" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L172" s="2" t="s">
+        <v>1752</v>
+      </c>
+      <c r="M172" s="2" t="s">
+        <v>1753</v>
+      </c>
+      <c r="N172" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O172" s="2" t="s">
+        <v>1754</v>
+      </c>
+      <c r="P172" s="2" t="s">
+        <v>1755</v>
+      </c>
+      <c r="Q172" s="2" t="s">
+        <v>1756</v>
+      </c>
+      <c r="R172" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S172" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T172" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U172" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V172" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W172" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="173" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A173" s="2" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B173" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C173" s="3">
+        <v>4</v>
+      </c>
+      <c r="D173" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E173" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>1758</v>
+      </c>
+      <c r="G173" s="2" t="s">
+        <v>1759</v>
+      </c>
+      <c r="H173" s="2" t="s">
+        <v>1760</v>
+      </c>
+      <c r="I173" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="J173" s="2" t="s">
+        <v>1762</v>
+      </c>
+      <c r="K173" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L173" s="2" t="s">
+        <v>1763</v>
+      </c>
+      <c r="M173" s="2" t="s">
+        <v>1764</v>
+      </c>
+      <c r="N173" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="O173" s="2" t="s">
+        <v>1765</v>
+      </c>
+      <c r="P173" s="2" t="s">
+        <v>1766</v>
+      </c>
+      <c r="Q173" s="2" t="s">
+        <v>1767</v>
+      </c>
+      <c r="R173" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S173" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T173" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U173" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V173" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W173" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="174" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A174" s="2" t="s">
+        <v>1768</v>
+      </c>
+      <c r="B174" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C174" s="3">
+        <v>4</v>
+      </c>
+      <c r="D174" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E174" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>1769</v>
+      </c>
+      <c r="G174" s="2" t="s">
+        <v>1770</v>
+      </c>
+      <c r="H174" s="2" t="s">
+        <v>1771</v>
+      </c>
+      <c r="I174" s="2" t="s">
+        <v>1772</v>
+      </c>
+      <c r="J174" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="K174" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L174" s="2" t="s">
+        <v>1773</v>
+      </c>
+      <c r="M174" s="2" t="s">
+        <v>1774</v>
+      </c>
+      <c r="N174" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="O174" s="2" t="s">
+        <v>1775</v>
+      </c>
+      <c r="P174" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="Q174" s="2" t="s">
+        <v>1777</v>
+      </c>
+      <c r="R174" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S174" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T174" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U174" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V174" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W174" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="175" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A175" s="2" t="s">
+        <v>1778</v>
+      </c>
+      <c r="B175" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C175" s="3">
+        <v>4</v>
+      </c>
+      <c r="D175" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E175" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F175" s="2" t="s">
+        <v>1779</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>1780</v>
+      </c>
+      <c r="H175" s="2" t="s">
+        <v>1781</v>
+      </c>
+      <c r="I175" s="2" t="s">
+        <v>1782</v>
+      </c>
+      <c r="J175" s="2" t="s">
+        <v>1783</v>
+      </c>
+      <c r="K175" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L175" s="2" t="s">
+        <v>1784</v>
+      </c>
+      <c r="M175" s="2" t="s">
+        <v>1785</v>
+      </c>
+      <c r="N175" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O175" s="2" t="s">
+        <v>1786</v>
+      </c>
+      <c r="P175" s="2" t="s">
+        <v>1787</v>
+      </c>
+      <c r="Q175" s="2" t="s">
+        <v>1788</v>
+      </c>
+      <c r="R175" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S175" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T175" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U175" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V175" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W175" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="176" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A176" s="2" t="s">
+        <v>1789</v>
+      </c>
+      <c r="B176" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C176" s="3">
+        <v>4</v>
+      </c>
+      <c r="D176" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E176" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>1790</v>
+      </c>
+      <c r="G176" s="2" t="s">
+        <v>1791</v>
+      </c>
+      <c r="H176" s="2" t="s">
+        <v>1792</v>
+      </c>
+      <c r="I176" s="2" t="s">
+        <v>1793</v>
+      </c>
+      <c r="J176" s="2" t="s">
+        <v>1719</v>
+      </c>
+      <c r="K176" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L176" s="2" t="s">
+        <v>1794</v>
+      </c>
+      <c r="M176" s="2" t="s">
+        <v>1795</v>
+      </c>
+      <c r="N176" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O176" s="2" t="s">
+        <v>1796</v>
+      </c>
+      <c r="P176" s="2" t="s">
+        <v>1797</v>
+      </c>
+      <c r="Q176" s="2" t="s">
+        <v>1798</v>
+      </c>
+      <c r="R176" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S176" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T176" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U176" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V176" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W176" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="177" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A177" s="2" t="s">
+        <v>1799</v>
+      </c>
+      <c r="B177" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C177" s="3">
+        <v>4</v>
+      </c>
+      <c r="D177" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E177" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F177" s="2" t="s">
+        <v>1800</v>
+      </c>
+      <c r="G177" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>1801</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>1802</v>
+      </c>
+      <c r="J177" s="2" t="s">
+        <v>1803</v>
+      </c>
+      <c r="K177" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L177" s="2" t="s">
+        <v>1804</v>
+      </c>
+      <c r="M177" s="2" t="s">
+        <v>1805</v>
+      </c>
+      <c r="N177" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O177" s="2" t="s">
+        <v>1806</v>
+      </c>
+      <c r="P177" s="2" t="s">
+        <v>1807</v>
+      </c>
+      <c r="Q177" s="2" t="s">
+        <v>1808</v>
+      </c>
+      <c r="R177" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S177" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T177" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U177" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V177" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W177" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="178" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A178" s="2" t="s">
+        <v>1809</v>
+      </c>
+      <c r="B178" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C178" s="3">
+        <v>4</v>
+      </c>
+      <c r="D178" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E178" s="2" t="s">
+        <v>1345</v>
+      </c>
+      <c r="F178" s="2" t="s">
+        <v>1810</v>
+      </c>
+      <c r="G178" s="2" t="s">
+        <v>1811</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>1369</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>1368</v>
+      </c>
+      <c r="J178" s="2" t="s">
+        <v>1812</v>
+      </c>
+      <c r="K178" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L178" s="2" t="s">
+        <v>1813</v>
+      </c>
+      <c r="M178" s="2" t="s">
+        <v>1814</v>
+      </c>
+      <c r="N178" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O178" s="2" t="s">
+        <v>1815</v>
+      </c>
+      <c r="P178" s="2" t="s">
+        <v>1816</v>
+      </c>
+      <c r="Q178" s="2" t="s">
+        <v>1817</v>
+      </c>
+      <c r="R178" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S178" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T178" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U178" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V178" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W178" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="179" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A179" s="2" t="s">
+        <v>1818</v>
+      </c>
+      <c r="B179" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C179" s="3">
+        <v>4</v>
+      </c>
+      <c r="D179" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E179" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F179" s="2" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G179" s="2" t="s">
+        <v>848</v>
+      </c>
+      <c r="H179" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="I179" s="2" t="s">
+        <v>1445</v>
+      </c>
+      <c r="J179" s="2" t="s">
+        <v>1821</v>
+      </c>
+      <c r="K179" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L179" s="2" t="s">
+        <v>1822</v>
+      </c>
+      <c r="M179" s="2" t="s">
+        <v>1823</v>
+      </c>
+      <c r="N179" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O179" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="P179" s="2" t="s">
+        <v>1824</v>
+      </c>
+      <c r="Q179" s="2" t="s">
+        <v>1825</v>
+      </c>
+      <c r="R179" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S179" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T179" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U179" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V179" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W179" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="180" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A180" s="2" t="s">
+        <v>1826</v>
+      </c>
+      <c r="B180" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C180" s="3">
+        <v>4</v>
+      </c>
+      <c r="D180" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E180" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F180" s="2" t="s">
+        <v>1827</v>
+      </c>
+      <c r="G180" s="2" t="s">
+        <v>1828</v>
+      </c>
+      <c r="H180" s="2" t="s">
+        <v>1576</v>
+      </c>
+      <c r="I180" s="2" t="s">
+        <v>1499</v>
+      </c>
+      <c r="J180" s="2" t="s">
+        <v>1829</v>
+      </c>
+      <c r="K180" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L180" s="2" t="s">
+        <v>1830</v>
+      </c>
+      <c r="M180" s="2" t="s">
+        <v>1831</v>
+      </c>
+      <c r="N180" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O180" s="2" t="s">
+        <v>1832</v>
+      </c>
+      <c r="P180" s="2" t="s">
+        <v>1833</v>
+      </c>
+      <c r="Q180" s="2" t="s">
+        <v>1834</v>
+      </c>
+      <c r="R180" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S180" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T180" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U180" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V180" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W180" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="181" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A181" s="2" t="s">
+        <v>1835</v>
+      </c>
+      <c r="B181" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C181" s="3">
+        <v>4</v>
+      </c>
+      <c r="D181" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E181" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F181" s="2" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G181" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="H181" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="I181" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="J181" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="K181" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L181" s="2" t="s">
+        <v>1837</v>
+      </c>
+      <c r="M181" s="2" t="s">
+        <v>1838</v>
+      </c>
+      <c r="N181" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O181" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P181" s="2" t="s">
+        <v>1839</v>
+      </c>
+      <c r="Q181" s="2" t="s">
+        <v>1840</v>
+      </c>
+      <c r="R181" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S181" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T181" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U181" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V181" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W181" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="182" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
+        <v>1841</v>
+      </c>
+      <c r="B182" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C182" s="3">
+        <v>4</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F182" s="2" t="s">
+        <v>1842</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="H182" s="2" t="s">
+        <v>1844</v>
+      </c>
+      <c r="I182" s="2" t="s">
+        <v>1845</v>
+      </c>
+      <c r="J182" s="2" t="s">
+        <v>1846</v>
+      </c>
+      <c r="K182" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L182" s="2" t="s">
+        <v>1847</v>
+      </c>
+      <c r="M182" s="2" t="s">
+        <v>1848</v>
+      </c>
+      <c r="N182" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O182" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="P182" s="2" t="s">
+        <v>1849</v>
+      </c>
+      <c r="Q182" s="2" t="s">
+        <v>1850</v>
+      </c>
+      <c r="R182" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S182" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T182" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U182" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V182" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W182" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="183" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A183" s="2" t="s">
+        <v>1851</v>
+      </c>
+      <c r="B183" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C183" s="3">
+        <v>4</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F183" s="2" t="s">
+        <v>1852</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="H183" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="I183" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="J183" s="2" t="s">
+        <v>1855</v>
+      </c>
+      <c r="K183" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L183" s="2" t="s">
+        <v>1856</v>
+      </c>
+      <c r="M183" s="2" t="s">
+        <v>1857</v>
+      </c>
+      <c r="N183" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O183" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="P183" s="2" t="s">
+        <v>1858</v>
+      </c>
+      <c r="Q183" s="2" t="s">
+        <v>1859</v>
+      </c>
+      <c r="R183" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S183" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T183" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U183" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V183" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W183" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="184" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
+        <v>1860</v>
+      </c>
+      <c r="B184" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C184" s="3">
+        <v>4</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F184" s="2" t="s">
+        <v>1861</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="I184" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="J184" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="K184" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L184" s="2" t="s">
+        <v>1865</v>
+      </c>
+      <c r="M184" s="2" t="s">
+        <v>1866</v>
+      </c>
+      <c r="N184" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O184" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="P184" s="2" t="s">
+        <v>1867</v>
+      </c>
+      <c r="Q184" s="2" t="s">
+        <v>1868</v>
+      </c>
+      <c r="R184" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S184" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T184" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U184" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V184" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W184" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="185" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A185" s="2" t="s">
+        <v>1869</v>
+      </c>
+      <c r="B185" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C185" s="3">
+        <v>4</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F185" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>1863</v>
+      </c>
+      <c r="I185" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="J185" s="2" t="s">
+        <v>1871</v>
+      </c>
+      <c r="K185" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L185" s="2" t="s">
+        <v>1872</v>
+      </c>
+      <c r="M185" s="2" t="s">
+        <v>1873</v>
+      </c>
+      <c r="N185" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O185" s="2" t="s">
+        <v>1874</v>
+      </c>
+      <c r="P185" s="2" t="s">
+        <v>1875</v>
+      </c>
+      <c r="Q185" s="2" t="s">
+        <v>1876</v>
+      </c>
+      <c r="R185" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S185" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T185" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U185" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V185" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W185" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="186" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A186" s="2" t="s">
+        <v>1877</v>
+      </c>
+      <c r="B186" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C186" s="3">
+        <v>4</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F186" s="2" t="s">
+        <v>1878</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="H186" s="2" t="s">
+        <v>1879</v>
+      </c>
+      <c r="I186" s="2" t="s">
+        <v>1854</v>
+      </c>
+      <c r="J186" s="2" t="s">
+        <v>1880</v>
+      </c>
+      <c r="K186" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L186" s="2" t="s">
+        <v>1881</v>
+      </c>
+      <c r="M186" s="2" t="s">
+        <v>1882</v>
+      </c>
+      <c r="N186" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O186" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="P186" s="2" t="s">
+        <v>1883</v>
+      </c>
+      <c r="Q186" s="2" t="s">
+        <v>1884</v>
+      </c>
+      <c r="R186" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S186" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T186" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U186" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V186" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W186" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="187" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A187" s="2" t="s">
+        <v>1885</v>
+      </c>
+      <c r="B187" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C187" s="3">
+        <v>4</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F187" s="2" t="s">
+        <v>1886</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>1862</v>
+      </c>
+      <c r="H187" s="2" t="s">
+        <v>1740</v>
+      </c>
+      <c r="I187" s="2" t="s">
+        <v>1887</v>
+      </c>
+      <c r="J187" s="2" t="s">
+        <v>1864</v>
+      </c>
+      <c r="K187" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L187" s="2" t="s">
+        <v>1888</v>
+      </c>
+      <c r="M187" s="2" t="s">
+        <v>1889</v>
+      </c>
+      <c r="N187" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O187" s="2" t="s">
+        <v>1515</v>
+      </c>
+      <c r="P187" s="2" t="s">
+        <v>1890</v>
+      </c>
+      <c r="Q187" s="2" t="s">
+        <v>1891</v>
+      </c>
+      <c r="R187" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S187" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T187" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U187" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V187" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W187" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="188" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A188" s="2" t="s">
+        <v>1892</v>
+      </c>
+      <c r="B188" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C188" s="3">
+        <v>4</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F188" s="2" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="H188" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="I188" s="2" t="s">
+        <v>1895</v>
+      </c>
+      <c r="J188" s="2" t="s">
+        <v>1896</v>
+      </c>
+      <c r="K188" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L188" s="2" t="s">
+        <v>1897</v>
+      </c>
+      <c r="M188" s="2" t="s">
+        <v>1898</v>
+      </c>
+      <c r="N188" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O188" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="P188" s="2" t="s">
+        <v>1900</v>
+      </c>
+      <c r="Q188" s="2" t="s">
+        <v>1901</v>
+      </c>
+      <c r="R188" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S188" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T188" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U188" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V188" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W188" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="189" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A189" s="2" t="s">
+        <v>1902</v>
+      </c>
+      <c r="B189" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C189" s="3">
+        <v>4</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F189" s="2" t="s">
+        <v>1903</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>1843</v>
+      </c>
+      <c r="H189" s="2" t="s">
+        <v>1894</v>
+      </c>
+      <c r="I189" s="2" t="s">
+        <v>1853</v>
+      </c>
+      <c r="J189" s="2" t="s">
+        <v>1904</v>
+      </c>
+      <c r="K189" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L189" s="2" t="s">
+        <v>1905</v>
+      </c>
+      <c r="M189" s="2" t="s">
+        <v>1906</v>
+      </c>
+      <c r="N189" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O189" s="2" t="s">
+        <v>1899</v>
+      </c>
+      <c r="P189" s="2" t="s">
+        <v>1907</v>
+      </c>
+      <c r="Q189" s="2" t="s">
+        <v>1908</v>
+      </c>
+      <c r="R189" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S189" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T189" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U189" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V189" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W189" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="190" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A190" s="2" t="s">
+        <v>1909</v>
+      </c>
+      <c r="B190" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C190" s="3">
+        <v>4</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>1507</v>
+      </c>
+      <c r="F190" s="2" t="s">
+        <v>1910</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>846</v>
+      </c>
+      <c r="H190" s="2" t="s">
+        <v>1820</v>
+      </c>
+      <c r="I190" s="2" t="s">
+        <v>847</v>
+      </c>
+      <c r="J190" s="2" t="s">
+        <v>1911</v>
+      </c>
+      <c r="K190" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L190" s="2" t="s">
+        <v>1912</v>
+      </c>
+      <c r="M190" s="2" t="s">
+        <v>1913</v>
+      </c>
+      <c r="N190" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O190" s="2" t="s">
+        <v>1914</v>
+      </c>
+      <c r="P190" s="2" t="s">
+        <v>1915</v>
+      </c>
+      <c r="Q190" s="2" t="s">
+        <v>1916</v>
+      </c>
+      <c r="R190" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S190" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T190" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U190" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V190" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W190" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="191" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A191" s="2" t="s">
+        <v>1917</v>
+      </c>
+      <c r="B191" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C191" s="3">
+        <v>4</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F191" s="2" t="s">
+        <v>1918</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>1919</v>
+      </c>
+      <c r="H191" s="2" t="s">
+        <v>1920</v>
+      </c>
+      <c r="I191" s="2" t="s">
+        <v>1921</v>
+      </c>
+      <c r="J191" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="K191" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L191" s="2" t="s">
+        <v>1923</v>
+      </c>
+      <c r="M191" s="2" t="s">
+        <v>1924</v>
+      </c>
+      <c r="N191" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O191" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P191" s="2" t="s">
+        <v>1925</v>
+      </c>
+      <c r="Q191" s="2" t="s">
+        <v>1926</v>
+      </c>
+      <c r="R191" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S191" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T191" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U191" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V191" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W191" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="192" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A192" s="2" t="s">
+        <v>1927</v>
+      </c>
+      <c r="B192" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C192" s="3">
+        <v>4</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F192" s="2" t="s">
+        <v>1928</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>1929</v>
+      </c>
+      <c r="H192" s="2" t="s">
+        <v>1930</v>
+      </c>
+      <c r="I192" s="2" t="s">
+        <v>1931</v>
+      </c>
+      <c r="J192" s="2" t="s">
+        <v>1932</v>
+      </c>
+      <c r="K192" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L192" s="2" t="s">
+        <v>1933</v>
+      </c>
+      <c r="M192" s="2" t="s">
+        <v>1934</v>
+      </c>
+      <c r="N192" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O192" s="2" t="s">
+        <v>1935</v>
+      </c>
+      <c r="P192" s="2" t="s">
+        <v>1936</v>
+      </c>
+      <c r="Q192" s="2" t="s">
+        <v>1937</v>
+      </c>
+      <c r="R192" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S192" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T192" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U192" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V192" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W192" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="193" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A193" s="2" t="s">
+        <v>1938</v>
+      </c>
+      <c r="B193" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C193" s="3">
+        <v>4</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F193" s="2" t="s">
+        <v>1939</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H193" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="I193" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="J193" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="K193" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L193" s="2" t="s">
+        <v>1943</v>
+      </c>
+      <c r="M193" s="2" t="s">
+        <v>1944</v>
+      </c>
+      <c r="N193" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O193" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="P193" s="2" t="s">
+        <v>1946</v>
+      </c>
+      <c r="Q193" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="R193" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S193" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T193" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U193" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V193" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W193" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="194" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A194" s="2" t="s">
+        <v>1948</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C194" s="3">
+        <v>4</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F194" s="2" t="s">
+        <v>1949</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>1950</v>
+      </c>
+      <c r="H194" s="2" t="s">
+        <v>1951</v>
+      </c>
+      <c r="I194" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="J194" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="K194" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L194" s="2" t="s">
+        <v>1953</v>
+      </c>
+      <c r="M194" s="2" t="s">
+        <v>1954</v>
+      </c>
+      <c r="N194" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O194" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="P194" s="2" t="s">
+        <v>1955</v>
+      </c>
+      <c r="Q194" s="2" t="s">
+        <v>1956</v>
+      </c>
+      <c r="R194" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S194" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T194" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U194" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V194" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W194" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="195" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A195" s="2" t="s">
+        <v>1957</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C195" s="3">
+        <v>4</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F195" s="2" t="s">
+        <v>1958</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>1959</v>
+      </c>
+      <c r="H195" s="2" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I195" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="J195" s="2" t="s">
+        <v>1960</v>
+      </c>
+      <c r="K195" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L195" s="2" t="s">
+        <v>1961</v>
+      </c>
+      <c r="M195" s="2" t="s">
+        <v>1962</v>
+      </c>
+      <c r="N195" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O195" s="2" t="s">
+        <v>1963</v>
+      </c>
+      <c r="P195" s="2" t="s">
+        <v>1964</v>
+      </c>
+      <c r="Q195" s="2" t="s">
+        <v>1965</v>
+      </c>
+      <c r="R195" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S195" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T195" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U195" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V195" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W195" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="196" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A196" s="2" t="s">
+        <v>1966</v>
+      </c>
+      <c r="B196" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C196" s="3">
+        <v>4</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F196" s="2" t="s">
+        <v>1967</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>1968</v>
+      </c>
+      <c r="H196" s="2" t="s">
+        <v>1969</v>
+      </c>
+      <c r="I196" s="2" t="s">
+        <v>1970</v>
+      </c>
+      <c r="J196" s="2" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K196" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L196" s="2" t="s">
+        <v>1971</v>
+      </c>
+      <c r="M196" s="2" t="s">
+        <v>1972</v>
+      </c>
+      <c r="N196" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O196" s="2" t="s">
+        <v>1973</v>
+      </c>
+      <c r="P196" s="2" t="s">
+        <v>1974</v>
+      </c>
+      <c r="Q196" s="2" t="s">
+        <v>1975</v>
+      </c>
+      <c r="R196" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S196" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T196" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U196" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V196" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W196" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="197" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A197" s="2" t="s">
+        <v>1976</v>
+      </c>
+      <c r="B197" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C197" s="3">
+        <v>4</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F197" s="2" t="s">
+        <v>1977</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H197" s="2" t="s">
+        <v>1978</v>
+      </c>
+      <c r="I197" s="2" t="s">
+        <v>1979</v>
+      </c>
+      <c r="J197" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="K197" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L197" s="2" t="s">
+        <v>1980</v>
+      </c>
+      <c r="M197" s="2" t="s">
+        <v>1981</v>
+      </c>
+      <c r="N197" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O197" s="2" t="s">
+        <v>757</v>
+      </c>
+      <c r="P197" s="2" t="s">
+        <v>1982</v>
+      </c>
+      <c r="Q197" s="2" t="s">
+        <v>1983</v>
+      </c>
+      <c r="R197" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S197" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T197" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U197" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V197" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W197" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="198" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A198" s="2" t="s">
+        <v>1984</v>
+      </c>
+      <c r="B198" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C198" s="3">
+        <v>4</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F198" s="2" t="s">
+        <v>1985</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>1986</v>
+      </c>
+      <c r="H198" s="2" t="s">
+        <v>1987</v>
+      </c>
+      <c r="I198" s="2" t="s">
+        <v>1988</v>
+      </c>
+      <c r="J198" s="2" t="s">
+        <v>1989</v>
+      </c>
+      <c r="K198" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L198" s="2" t="s">
+        <v>1990</v>
+      </c>
+      <c r="M198" s="2" t="s">
+        <v>1991</v>
+      </c>
+      <c r="N198" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O198" s="2" t="s">
+        <v>1992</v>
+      </c>
+      <c r="P198" s="2" t="s">
+        <v>1993</v>
+      </c>
+      <c r="Q198" s="2" t="s">
+        <v>1994</v>
+      </c>
+      <c r="R198" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S198" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T198" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U198" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V198" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W198" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="199" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A199" s="2" t="s">
+        <v>1995</v>
+      </c>
+      <c r="B199" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C199" s="3">
+        <v>4</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F199" s="2" t="s">
+        <v>1996</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>1997</v>
+      </c>
+      <c r="H199" s="2" t="s">
+        <v>1998</v>
+      </c>
+      <c r="I199" s="2" t="s">
+        <v>1999</v>
+      </c>
+      <c r="J199" s="2" t="s">
+        <v>2000</v>
+      </c>
+      <c r="K199" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L199" s="2" t="s">
+        <v>2001</v>
+      </c>
+      <c r="M199" s="2" t="s">
+        <v>2002</v>
+      </c>
+      <c r="N199" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O199" s="2" t="s">
+        <v>2003</v>
+      </c>
+      <c r="P199" s="2" t="s">
+        <v>2004</v>
+      </c>
+      <c r="Q199" s="2" t="s">
+        <v>2005</v>
+      </c>
+      <c r="R199" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S199" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T199" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U199" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V199" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W199" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="200" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A200" s="2" t="s">
+        <v>2006</v>
+      </c>
+      <c r="B200" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C200" s="3">
+        <v>4</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F200" s="2" t="s">
+        <v>2007</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>1695</v>
+      </c>
+      <c r="H200" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="I200" s="2" t="s">
+        <v>1696</v>
+      </c>
+      <c r="J200" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="K200" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L200" s="2" t="s">
+        <v>2008</v>
+      </c>
+      <c r="M200" s="2" t="s">
+        <v>2009</v>
+      </c>
+      <c r="N200" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O200" s="2" t="s">
+        <v>2010</v>
+      </c>
+      <c r="P200" s="2" t="s">
+        <v>2011</v>
+      </c>
+      <c r="Q200" s="2" t="s">
+        <v>2012</v>
+      </c>
+      <c r="R200" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S200" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T200" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U200" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V200" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W200" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="201" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A201" s="2" t="s">
+        <v>2013</v>
+      </c>
+      <c r="B201" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C201" s="3">
+        <v>4</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F201" s="2" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>2015</v>
+      </c>
+      <c r="H201" s="2" t="s">
+        <v>2016</v>
+      </c>
+      <c r="I201" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="J201" s="2" t="s">
+        <v>753</v>
+      </c>
+      <c r="K201" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L201" s="2" t="s">
+        <v>2017</v>
+      </c>
+      <c r="M201" s="2" t="s">
+        <v>2018</v>
+      </c>
+      <c r="N201" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O201" s="2" t="s">
+        <v>2019</v>
+      </c>
+      <c r="P201" s="2" t="s">
+        <v>2020</v>
+      </c>
+      <c r="Q201" s="2" t="s">
+        <v>2021</v>
+      </c>
+      <c r="R201" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S201" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T201" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U201" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V201" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W201" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="202" spans="1:23" ht="45" x14ac:dyDescent="0.3">
+      <c r="A202" s="2" t="s">
+        <v>2022</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C202" s="3">
+        <v>4</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F202" s="2" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>1922</v>
+      </c>
+      <c r="H202" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="I202" s="2" t="s">
+        <v>1941</v>
+      </c>
+      <c r="J202" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="K202" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L202" s="2" t="s">
+        <v>2024</v>
+      </c>
+      <c r="M202" s="2" t="s">
+        <v>2025</v>
+      </c>
+      <c r="N202" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O202" s="2" t="s">
+        <v>1945</v>
+      </c>
+      <c r="P202" s="2" t="s">
+        <v>2026</v>
+      </c>
+      <c r="Q202" s="2" t="s">
+        <v>1947</v>
+      </c>
+      <c r="R202" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S202" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T202" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U202" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V202" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W202" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="203" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A203" s="2" t="s">
+        <v>2027</v>
+      </c>
+      <c r="B203" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C203" s="3">
+        <v>4</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F203" s="2" t="s">
+        <v>2028</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>2029</v>
+      </c>
+      <c r="H203" s="2" t="s">
+        <v>2030</v>
+      </c>
+      <c r="I203" s="2" t="s">
+        <v>2031</v>
+      </c>
+      <c r="J203" s="2" t="s">
+        <v>2032</v>
+      </c>
+      <c r="K203" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L203" s="2" t="s">
+        <v>2033</v>
+      </c>
+      <c r="M203" s="2" t="s">
+        <v>2034</v>
+      </c>
+      <c r="N203" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O203" s="2" t="s">
+        <v>2035</v>
+      </c>
+      <c r="P203" s="2" t="s">
+        <v>2036</v>
+      </c>
+      <c r="Q203" s="2" t="s">
+        <v>2037</v>
+      </c>
+      <c r="R203" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S203" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T203" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U203" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V203" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W203" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="204" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A204" s="2" t="s">
+        <v>2038</v>
+      </c>
+      <c r="B204" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C204" s="3">
+        <v>4</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F204" s="2" t="s">
+        <v>2039</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>2040</v>
+      </c>
+      <c r="H204" s="2" t="s">
+        <v>1697</v>
+      </c>
+      <c r="I204" s="2" t="s">
+        <v>2041</v>
+      </c>
+      <c r="J204" s="2" t="s">
+        <v>2042</v>
+      </c>
+      <c r="K204" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L204" s="2" t="s">
+        <v>2043</v>
+      </c>
+      <c r="M204" s="2" t="s">
+        <v>2044</v>
+      </c>
+      <c r="N204" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O204" s="2" t="s">
+        <v>2035</v>
+      </c>
+      <c r="P204" s="2" t="s">
+        <v>2045</v>
+      </c>
+      <c r="Q204" s="2" t="s">
+        <v>2046</v>
+      </c>
+      <c r="R204" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S204" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T204" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U204" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V204" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W204" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="205" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A205" s="2" t="s">
+        <v>2047</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C205" s="3">
+        <v>4</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F205" s="2" t="s">
+        <v>2048</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>2049</v>
+      </c>
+      <c r="H205" s="2" t="s">
+        <v>2050</v>
+      </c>
+      <c r="I205" s="2" t="s">
+        <v>2051</v>
+      </c>
+      <c r="J205" s="2" t="s">
+        <v>1694</v>
+      </c>
+      <c r="K205" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L205" s="2" t="s">
+        <v>2052</v>
+      </c>
+      <c r="M205" s="2" t="s">
+        <v>2053</v>
+      </c>
+      <c r="N205" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O205" s="2" t="s">
+        <v>2035</v>
+      </c>
+      <c r="P205" s="2" t="s">
+        <v>2054</v>
+      </c>
+      <c r="Q205" s="2" t="s">
+        <v>2055</v>
+      </c>
+      <c r="R205" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S205" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T205" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U205" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V205" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W205" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="206" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A206" s="2" t="s">
+        <v>2056</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C206" s="3">
+        <v>4</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F206" s="2" t="s">
+        <v>2057</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>1942</v>
+      </c>
+      <c r="H206" s="2" t="s">
+        <v>1952</v>
+      </c>
+      <c r="I206" s="2" t="s">
+        <v>1940</v>
+      </c>
+      <c r="J206" s="2" t="s">
+        <v>2058</v>
+      </c>
+      <c r="K206" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L206" s="2" t="s">
+        <v>2059</v>
+      </c>
+      <c r="M206" s="2" t="s">
+        <v>2060</v>
+      </c>
+      <c r="N206" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O206" s="2" t="s">
+        <v>2019</v>
+      </c>
+      <c r="P206" s="2" t="s">
+        <v>2061</v>
+      </c>
+      <c r="Q206" s="2" t="s">
+        <v>2062</v>
+      </c>
+      <c r="R206" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S206" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T206" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U206" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V206" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W206" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="207" spans="1:23" ht="75" x14ac:dyDescent="0.3">
+      <c r="A207" s="2" t="s">
+        <v>2063</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C207" s="3">
+        <v>4</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F207" s="2" t="s">
+        <v>2064</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>1423</v>
+      </c>
+      <c r="H207" s="2" t="s">
+        <v>1426</v>
+      </c>
+      <c r="I207" s="2" t="s">
+        <v>2065</v>
+      </c>
+      <c r="J207" s="2" t="s">
+        <v>2066</v>
+      </c>
+      <c r="K207" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L207" s="2" t="s">
+        <v>2067</v>
+      </c>
+      <c r="M207" s="2" t="s">
+        <v>2068</v>
+      </c>
+      <c r="N207" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O207" s="2" t="s">
+        <v>2035</v>
+      </c>
+      <c r="P207" s="2" t="s">
+        <v>2069</v>
+      </c>
+      <c r="Q207" s="2" t="s">
+        <v>2070</v>
+      </c>
+      <c r="R207" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S207" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T207" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U207" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V207" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W207" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="208" spans="1:23" ht="60" x14ac:dyDescent="0.3">
+      <c r="A208" s="2" t="s">
+        <v>2071</v>
+      </c>
+      <c r="B208" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C208" s="3">
+        <v>4</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>1344</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>1600</v>
+      </c>
+      <c r="F208" s="2" t="s">
+        <v>2072</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>2073</v>
+      </c>
+      <c r="H208" s="2" t="s">
+        <v>2074</v>
+      </c>
+      <c r="I208" s="2" t="s">
+        <v>2075</v>
+      </c>
+      <c r="J208" s="2" t="s">
+        <v>2076</v>
+      </c>
+      <c r="K208" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="L208" s="2" t="s">
+        <v>2077</v>
+      </c>
+      <c r="M208" s="2" t="s">
+        <v>2078</v>
+      </c>
+      <c r="N208" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="O208" s="2" t="s">
+        <v>1608</v>
+      </c>
+      <c r="P208" s="2" t="s">
+        <v>2079</v>
+      </c>
+      <c r="Q208" s="2" t="s">
+        <v>2080</v>
+      </c>
+      <c r="R208" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="S208" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="T208" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="U208" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="V208" s="2" t="s">
+        <v>1354</v>
+      </c>
+      <c r="W208" s="2" t="s">
+        <v>42</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:W39" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
